--- a/data/umr/Resumen UMR Octubre 2026.xlsx
+++ b/data/umr/Resumen UMR Octubre 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E604752-E33A-4E6F-9C86-E7587F649DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0783BC91-FFCA-408E-84AC-4C77B876054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,7 +1155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="193">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -2123,7 +2123,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="64">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2502,8 +2502,20 @@
         <bgColor indexed="60"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFDFD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="85">
+  <borders count="86">
     <border>
       <left/>
       <right/>
@@ -3539,6 +3551,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3626,7 +3653,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="389">
+  <cellXfs count="391">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -4547,6 +4574,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5808,37 +5841,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="350" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="350"/>
-      <c r="C1" s="350"/>
-      <c r="D1" s="350"/>
-      <c r="E1" s="350"/>
-      <c r="F1" s="350"/>
-      <c r="G1" s="350"/>
-      <c r="H1" s="350"/>
-      <c r="I1" s="350"/>
-      <c r="J1" s="350"/>
-      <c r="K1" s="350"/>
-      <c r="L1" s="350"/>
-      <c r="M1" s="350"/>
-      <c r="N1" s="350"/>
-      <c r="O1" s="350"/>
-      <c r="P1" s="350"/>
-      <c r="Q1" s="350"/>
-      <c r="R1" s="350"/>
-      <c r="S1" s="350"/>
-      <c r="T1" s="350"/>
-      <c r="U1" s="350"/>
-      <c r="V1" s="350"/>
-      <c r="W1" s="350"/>
-      <c r="X1" s="350"/>
-      <c r="Y1" s="350"/>
-      <c r="Z1" s="350"/>
-      <c r="AA1" s="350"/>
-      <c r="AB1" s="350"/>
-      <c r="AC1" s="350"/>
+      <c r="A1" s="352" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="352"/>
+      <c r="C1" s="352"/>
+      <c r="D1" s="352"/>
+      <c r="E1" s="352"/>
+      <c r="F1" s="352"/>
+      <c r="G1" s="352"/>
+      <c r="H1" s="352"/>
+      <c r="I1" s="352"/>
+      <c r="J1" s="352"/>
+      <c r="K1" s="352"/>
+      <c r="L1" s="352"/>
+      <c r="M1" s="352"/>
+      <c r="N1" s="352"/>
+      <c r="O1" s="352"/>
+      <c r="P1" s="352"/>
+      <c r="Q1" s="352"/>
+      <c r="R1" s="352"/>
+      <c r="S1" s="352"/>
+      <c r="T1" s="352"/>
+      <c r="U1" s="352"/>
+      <c r="V1" s="352"/>
+      <c r="W1" s="352"/>
+      <c r="X1" s="352"/>
+      <c r="Y1" s="352"/>
+      <c r="Z1" s="352"/>
+      <c r="AA1" s="352"/>
+      <c r="AB1" s="352"/>
+      <c r="AC1" s="352"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -6212,8 +6245,12 @@
       <c r="AA5" s="302">
         <v>2173263</v>
       </c>
-      <c r="AB5" s="302"/>
-      <c r="AC5" s="302"/>
+      <c r="AB5" s="222">
+        <v>2173779</v>
+      </c>
+      <c r="AC5" s="222">
+        <v>2174229</v>
+      </c>
       <c r="AD5" s="302"/>
       <c r="AE5" s="302"/>
       <c r="AF5" s="302"/>
@@ -6300,8 +6337,12 @@
       <c r="AA6" s="302">
         <v>2137586</v>
       </c>
-      <c r="AB6" s="302"/>
-      <c r="AC6" s="302"/>
+      <c r="AB6" s="222">
+        <v>2137953</v>
+      </c>
+      <c r="AC6" s="222">
+        <v>2138490</v>
+      </c>
       <c r="AD6" s="302"/>
       <c r="AE6" s="302"/>
       <c r="AF6" s="302"/>
@@ -6388,8 +6429,12 @@
       <c r="AA7" s="302">
         <v>2218585</v>
       </c>
-      <c r="AB7" s="302"/>
-      <c r="AC7" s="302"/>
+      <c r="AB7" s="222">
+        <v>2218847</v>
+      </c>
+      <c r="AC7" s="222">
+        <v>2219111</v>
+      </c>
       <c r="AD7" s="302"/>
       <c r="AE7" s="302"/>
       <c r="AF7" s="302"/>
@@ -6476,8 +6521,12 @@
       <c r="AA8" s="302">
         <v>2225800</v>
       </c>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="302"/>
+      <c r="AB8" s="222">
+        <v>2226323</v>
+      </c>
+      <c r="AC8" s="222">
+        <v>2226532</v>
+      </c>
       <c r="AD8" s="302"/>
       <c r="AE8" s="302"/>
       <c r="AF8" s="302"/>
@@ -6564,8 +6613,12 @@
       <c r="AA9" s="302">
         <v>2145056</v>
       </c>
-      <c r="AB9" s="302"/>
-      <c r="AC9" s="302"/>
+      <c r="AB9" s="222">
+        <v>2145384</v>
+      </c>
+      <c r="AC9" s="222">
+        <v>2145633</v>
+      </c>
       <c r="AD9" s="302"/>
       <c r="AE9" s="302"/>
       <c r="AF9" s="302"/>
@@ -6652,8 +6705,12 @@
       <c r="AA10" s="302">
         <v>2230014</v>
       </c>
-      <c r="AB10" s="302"/>
-      <c r="AC10" s="302"/>
+      <c r="AB10" s="222">
+        <v>2230107</v>
+      </c>
+      <c r="AC10" s="222">
+        <v>2230179</v>
+      </c>
       <c r="AD10" s="302"/>
       <c r="AE10" s="302"/>
       <c r="AF10" s="302"/>
@@ -6740,8 +6797,12 @@
       <c r="AA11" s="302">
         <v>2286727</v>
       </c>
-      <c r="AB11" s="302"/>
-      <c r="AC11" s="302"/>
+      <c r="AB11" s="222">
+        <v>2286902</v>
+      </c>
+      <c r="AC11" s="222">
+        <v>2287078</v>
+      </c>
       <c r="AD11" s="302"/>
       <c r="AE11" s="302"/>
       <c r="AF11" s="302"/>
@@ -6828,8 +6889,12 @@
       <c r="AA12" s="302">
         <v>2179269</v>
       </c>
-      <c r="AB12" s="302"/>
-      <c r="AC12" s="302"/>
+      <c r="AB12" s="222">
+        <v>2179829</v>
+      </c>
+      <c r="AC12" s="222">
+        <v>2180094</v>
+      </c>
       <c r="AD12" s="302"/>
       <c r="AE12" s="302"/>
       <c r="AF12" s="302"/>
@@ -6916,8 +6981,12 @@
       <c r="AA13" s="302">
         <v>2166370</v>
       </c>
-      <c r="AB13" s="302"/>
-      <c r="AC13" s="302"/>
+      <c r="AB13" s="222">
+        <v>2166564</v>
+      </c>
+      <c r="AC13" s="222">
+        <v>2166745</v>
+      </c>
       <c r="AD13" s="302"/>
       <c r="AE13" s="302"/>
       <c r="AF13" s="302"/>
@@ -7004,8 +7073,12 @@
       <c r="AA14" s="302">
         <v>2230095</v>
       </c>
-      <c r="AB14" s="302"/>
-      <c r="AC14" s="302"/>
+      <c r="AB14" s="222">
+        <v>2230613</v>
+      </c>
+      <c r="AC14" s="222">
+        <v>2231172</v>
+      </c>
       <c r="AD14" s="302"/>
       <c r="AE14" s="302"/>
       <c r="AF14" s="302"/>
@@ -7092,8 +7165,12 @@
       <c r="AA15" s="302">
         <v>2264448</v>
       </c>
-      <c r="AB15" s="302"/>
-      <c r="AC15" s="302"/>
+      <c r="AB15" s="222">
+        <v>2264468</v>
+      </c>
+      <c r="AC15" s="222">
+        <v>2264719</v>
+      </c>
       <c r="AD15" s="302"/>
       <c r="AE15" s="302"/>
       <c r="AF15" s="302"/>
@@ -7180,8 +7257,12 @@
       <c r="AA16" s="302">
         <v>2111383</v>
       </c>
-      <c r="AB16" s="302"/>
-      <c r="AC16" s="302"/>
+      <c r="AB16" s="222">
+        <v>2111585</v>
+      </c>
+      <c r="AC16" s="222">
+        <v>2112105</v>
+      </c>
       <c r="AD16" s="302"/>
       <c r="AE16" s="302"/>
       <c r="AF16" s="302"/>
@@ -7268,8 +7349,12 @@
       <c r="AA17" s="302">
         <v>2199230</v>
       </c>
-      <c r="AB17" s="302"/>
-      <c r="AC17" s="302"/>
+      <c r="AB17" s="222">
+        <v>2199422</v>
+      </c>
+      <c r="AC17" s="222">
+        <v>2199738</v>
+      </c>
       <c r="AD17" s="302"/>
       <c r="AE17" s="302"/>
       <c r="AF17" s="302"/>
@@ -7356,8 +7441,12 @@
       <c r="AA18" s="302">
         <v>2188310</v>
       </c>
-      <c r="AB18" s="302"/>
-      <c r="AC18" s="302"/>
+      <c r="AB18" s="222">
+        <v>2188870</v>
+      </c>
+      <c r="AC18" s="222">
+        <v>2189386</v>
+      </c>
       <c r="AD18" s="302"/>
       <c r="AE18" s="302"/>
       <c r="AF18" s="302"/>
@@ -7444,8 +7533,12 @@
       <c r="AA19" s="302">
         <v>2260050</v>
       </c>
-      <c r="AB19" s="302"/>
-      <c r="AC19" s="302"/>
+      <c r="AB19" s="222">
+        <v>2260613</v>
+      </c>
+      <c r="AC19" s="222">
+        <v>2261108</v>
+      </c>
       <c r="AD19" s="302"/>
       <c r="AE19" s="302"/>
       <c r="AF19" s="302"/>
@@ -7532,8 +7625,12 @@
       <c r="AA20" s="302">
         <v>2241992</v>
       </c>
-      <c r="AB20" s="302"/>
-      <c r="AC20" s="302"/>
+      <c r="AB20" s="222">
+        <v>2242596</v>
+      </c>
+      <c r="AC20" s="222">
+        <v>2243202</v>
+      </c>
       <c r="AD20" s="302"/>
       <c r="AE20" s="302"/>
       <c r="AF20" s="302"/>
@@ -7620,8 +7717,12 @@
       <c r="AA21" s="302">
         <v>2254637</v>
       </c>
-      <c r="AB21" s="302"/>
-      <c r="AC21" s="302"/>
+      <c r="AB21" s="222">
+        <v>2255157</v>
+      </c>
+      <c r="AC21" s="222">
+        <v>2255524</v>
+      </c>
       <c r="AD21" s="302"/>
       <c r="AE21" s="302"/>
       <c r="AF21" s="302"/>
@@ -7708,8 +7809,12 @@
       <c r="AA22" s="302">
         <v>2179842</v>
       </c>
-      <c r="AB22" s="302"/>
-      <c r="AC22" s="302"/>
+      <c r="AB22" s="222">
+        <v>2180096</v>
+      </c>
+      <c r="AC22" s="222">
+        <v>2180274</v>
+      </c>
       <c r="AD22" s="302"/>
       <c r="AE22" s="302"/>
       <c r="AF22" s="302"/>
@@ -7796,8 +7901,12 @@
       <c r="AA23" s="302">
         <v>2209908</v>
       </c>
-      <c r="AB23" s="302"/>
-      <c r="AC23" s="302"/>
+      <c r="AB23" s="222">
+        <v>2210306</v>
+      </c>
+      <c r="AC23" s="222">
+        <v>2210826</v>
+      </c>
       <c r="AD23" s="302"/>
       <c r="AE23" s="302"/>
       <c r="AF23" s="302"/>
@@ -7884,8 +7993,12 @@
       <c r="AA24" s="302">
         <v>2250302</v>
       </c>
-      <c r="AB24" s="302"/>
-      <c r="AC24" s="302"/>
+      <c r="AB24" s="222">
+        <v>2250495</v>
+      </c>
+      <c r="AC24" s="222">
+        <v>2251031</v>
+      </c>
       <c r="AD24" s="302"/>
       <c r="AE24" s="302"/>
       <c r="AF24" s="302"/>
@@ -7972,8 +8085,12 @@
       <c r="AA25" s="302">
         <v>2263413</v>
       </c>
-      <c r="AB25" s="302"/>
-      <c r="AC25" s="302"/>
+      <c r="AB25" s="222">
+        <v>2263663</v>
+      </c>
+      <c r="AC25" s="222">
+        <v>2263924</v>
+      </c>
       <c r="AD25" s="302"/>
       <c r="AE25" s="302"/>
       <c r="AF25" s="302"/>
@@ -8060,8 +8177,12 @@
       <c r="AA26" s="302">
         <v>2250232</v>
       </c>
-      <c r="AB26" s="302"/>
-      <c r="AC26" s="302"/>
+      <c r="AB26" s="222">
+        <v>2250400</v>
+      </c>
+      <c r="AC26" s="222">
+        <v>2250834</v>
+      </c>
       <c r="AD26" s="302"/>
       <c r="AE26" s="302"/>
       <c r="AF26" s="302"/>
@@ -8148,8 +8269,12 @@
       <c r="AA27" s="302">
         <v>2229254</v>
       </c>
-      <c r="AB27" s="302"/>
-      <c r="AC27" s="302"/>
+      <c r="AB27" s="222">
+        <v>2229687</v>
+      </c>
+      <c r="AC27" s="222">
+        <v>2229880</v>
+      </c>
       <c r="AD27" s="302"/>
       <c r="AE27" s="302"/>
       <c r="AF27" s="302"/>
@@ -8236,8 +8361,12 @@
       <c r="AA28" s="302">
         <v>2190501</v>
       </c>
-      <c r="AB28" s="302"/>
-      <c r="AC28" s="302"/>
+      <c r="AB28" s="222">
+        <v>2190740</v>
+      </c>
+      <c r="AC28" s="222">
+        <v>2190931</v>
+      </c>
       <c r="AD28" s="302"/>
       <c r="AE28" s="302"/>
       <c r="AF28" s="302"/>
@@ -8324,8 +8453,12 @@
       <c r="AA29" s="302">
         <v>2143911</v>
       </c>
-      <c r="AB29" s="302"/>
-      <c r="AC29" s="302"/>
+      <c r="AB29" s="222">
+        <v>2144191</v>
+      </c>
+      <c r="AC29" s="222">
+        <v>2144443</v>
+      </c>
       <c r="AD29" s="302"/>
       <c r="AE29" s="302"/>
       <c r="AF29" s="302"/>
@@ -8412,8 +8545,12 @@
       <c r="AA30" s="302">
         <v>1901172</v>
       </c>
-      <c r="AB30" s="302"/>
-      <c r="AC30" s="302"/>
+      <c r="AB30" s="222">
+        <v>1901732</v>
+      </c>
+      <c r="AC30" s="222">
+        <v>1902028</v>
+      </c>
       <c r="AD30" s="302"/>
       <c r="AE30" s="302"/>
       <c r="AF30" s="302"/>
@@ -8500,8 +8637,12 @@
       <c r="AA31" s="302">
         <v>2196430</v>
       </c>
-      <c r="AB31" s="302"/>
-      <c r="AC31" s="302"/>
+      <c r="AB31" s="222">
+        <v>2196680</v>
+      </c>
+      <c r="AC31" s="222">
+        <v>2196898</v>
+      </c>
       <c r="AD31" s="302"/>
       <c r="AE31" s="302"/>
       <c r="AF31" s="302"/>
@@ -8588,8 +8729,12 @@
       <c r="AA32" s="302">
         <v>785567</v>
       </c>
-      <c r="AB32" s="302"/>
-      <c r="AC32" s="302"/>
+      <c r="AB32" s="222">
+        <v>785863</v>
+      </c>
+      <c r="AC32" s="222">
+        <v>786255</v>
+      </c>
       <c r="AD32" s="302"/>
       <c r="AE32" s="302"/>
       <c r="AF32" s="302"/>
@@ -8676,8 +8821,12 @@
       <c r="AA33" s="302">
         <v>715627</v>
       </c>
-      <c r="AB33" s="302"/>
-      <c r="AC33" s="302"/>
+      <c r="AB33" s="222">
+        <v>715991</v>
+      </c>
+      <c r="AC33" s="222">
+        <v>716511</v>
+      </c>
       <c r="AD33" s="302"/>
       <c r="AE33" s="302"/>
       <c r="AF33" s="302"/>
@@ -8764,8 +8913,12 @@
       <c r="AA34" s="302">
         <v>751907</v>
       </c>
-      <c r="AB34" s="302"/>
-      <c r="AC34" s="302"/>
+      <c r="AB34" s="222">
+        <v>752348</v>
+      </c>
+      <c r="AC34" s="222">
+        <v>752586</v>
+      </c>
       <c r="AD34" s="302"/>
       <c r="AE34" s="302"/>
       <c r="AF34" s="302"/>
@@ -8852,8 +9005,12 @@
       <c r="AA35" s="302">
         <v>779481</v>
       </c>
-      <c r="AB35" s="302"/>
-      <c r="AC35" s="302"/>
+      <c r="AB35" s="222">
+        <v>779913</v>
+      </c>
+      <c r="AC35" s="222">
+        <v>780280</v>
+      </c>
       <c r="AD35" s="302"/>
       <c r="AE35" s="302"/>
       <c r="AF35" s="302"/>
@@ -8940,8 +9097,12 @@
       <c r="AA36" s="302">
         <v>753957</v>
       </c>
-      <c r="AB36" s="302"/>
-      <c r="AC36" s="302"/>
+      <c r="AB36" s="222">
+        <v>754478</v>
+      </c>
+      <c r="AC36" s="222">
+        <v>754996</v>
+      </c>
       <c r="AD36" s="302"/>
       <c r="AE36" s="302"/>
       <c r="AF36" s="302"/>
@@ -9028,8 +9189,12 @@
       <c r="AA37" s="302">
         <v>795972</v>
       </c>
-      <c r="AB37" s="302"/>
-      <c r="AC37" s="302"/>
+      <c r="AB37" s="222">
+        <v>796337</v>
+      </c>
+      <c r="AC37" s="222">
+        <v>796771</v>
+      </c>
       <c r="AD37" s="302"/>
       <c r="AE37" s="302"/>
       <c r="AF37" s="302"/>
@@ -9116,8 +9281,12 @@
       <c r="AA38" s="302">
         <v>441306</v>
       </c>
-      <c r="AB38" s="302"/>
-      <c r="AC38" s="302"/>
+      <c r="AB38" s="222">
+        <v>441611</v>
+      </c>
+      <c r="AC38" s="222">
+        <v>442171</v>
+      </c>
       <c r="AD38" s="302"/>
       <c r="AE38" s="302"/>
       <c r="AF38" s="302"/>
@@ -9204,8 +9373,12 @@
       <c r="AA39" s="302">
         <v>770439</v>
       </c>
-      <c r="AB39" s="302"/>
-      <c r="AC39" s="302"/>
+      <c r="AB39" s="222">
+        <v>771000</v>
+      </c>
+      <c r="AC39" s="222">
+        <v>771221</v>
+      </c>
       <c r="AD39" s="302"/>
       <c r="AE39" s="302"/>
       <c r="AF39" s="302"/>
@@ -9292,8 +9465,12 @@
       <c r="AA40" s="302">
         <v>8863</v>
       </c>
-      <c r="AB40" s="302"/>
-      <c r="AC40" s="302"/>
+      <c r="AB40" s="222">
+        <v>9068</v>
+      </c>
+      <c r="AC40" s="222">
+        <v>9408</v>
+      </c>
       <c r="AD40" s="302"/>
       <c r="AE40" s="302"/>
       <c r="AF40" s="302"/>
@@ -9380,8 +9557,12 @@
       <c r="AA41" s="302">
         <v>7178</v>
       </c>
-      <c r="AB41" s="302"/>
-      <c r="AC41" s="302"/>
+      <c r="AB41" s="222">
+        <v>7417</v>
+      </c>
+      <c r="AC41" s="222">
+        <v>7591</v>
+      </c>
       <c r="AD41" s="302"/>
       <c r="AE41" s="302"/>
       <c r="AF41" s="302"/>
@@ -9468,8 +9649,12 @@
       <c r="AA42" s="302">
         <v>31177</v>
       </c>
-      <c r="AB42" s="302"/>
-      <c r="AC42" s="302"/>
+      <c r="AB42" s="222">
+        <v>31493</v>
+      </c>
+      <c r="AC42" s="222">
+        <v>31851</v>
+      </c>
       <c r="AD42" s="302"/>
       <c r="AE42" s="302"/>
       <c r="AF42" s="302"/>
@@ -9556,8 +9741,12 @@
       <c r="AA43" s="302">
         <v>2239</v>
       </c>
-      <c r="AB43" s="302"/>
-      <c r="AC43" s="302"/>
+      <c r="AB43" s="222">
+        <v>2239</v>
+      </c>
+      <c r="AC43" s="222">
+        <v>2239</v>
+      </c>
       <c r="AD43" s="302"/>
       <c r="AE43" s="302"/>
       <c r="AF43" s="302"/>
@@ -9644,8 +9833,12 @@
       <c r="AA44" s="302">
         <v>2123</v>
       </c>
-      <c r="AB44" s="302"/>
-      <c r="AC44" s="302"/>
+      <c r="AB44" s="222">
+        <v>2123</v>
+      </c>
+      <c r="AC44" s="222">
+        <v>2123</v>
+      </c>
       <c r="AD44" s="302"/>
       <c r="AE44" s="302"/>
       <c r="AF44" s="302"/>
@@ -9680,37 +9873,37 @@
       <c r="AC45" s="209"/>
     </row>
     <row r="46" spans="1:32" ht="18" x14ac:dyDescent="0.25">
-      <c r="A46" s="350" t="s">
+      <c r="A46" s="352" t="s">
         <v>31</v>
       </c>
-      <c r="B46" s="350"/>
-      <c r="C46" s="350"/>
-      <c r="D46" s="350"/>
-      <c r="E46" s="350"/>
-      <c r="F46" s="350"/>
-      <c r="G46" s="350"/>
-      <c r="H46" s="350"/>
-      <c r="I46" s="350"/>
-      <c r="J46" s="350"/>
-      <c r="K46" s="350"/>
-      <c r="L46" s="350"/>
-      <c r="M46" s="350"/>
-      <c r="N46" s="350"/>
-      <c r="O46" s="350"/>
-      <c r="P46" s="350"/>
-      <c r="Q46" s="350"/>
-      <c r="R46" s="350"/>
-      <c r="S46" s="350"/>
-      <c r="T46" s="350"/>
-      <c r="U46" s="350"/>
-      <c r="V46" s="350"/>
-      <c r="W46" s="350"/>
-      <c r="X46" s="350"/>
-      <c r="Y46" s="350"/>
-      <c r="Z46" s="350"/>
-      <c r="AA46" s="350"/>
-      <c r="AB46" s="350"/>
-      <c r="AC46" s="350"/>
+      <c r="B46" s="352"/>
+      <c r="C46" s="352"/>
+      <c r="D46" s="352"/>
+      <c r="E46" s="352"/>
+      <c r="F46" s="352"/>
+      <c r="G46" s="352"/>
+      <c r="H46" s="352"/>
+      <c r="I46" s="352"/>
+      <c r="J46" s="352"/>
+      <c r="K46" s="352"/>
+      <c r="L46" s="352"/>
+      <c r="M46" s="352"/>
+      <c r="N46" s="352"/>
+      <c r="O46" s="352"/>
+      <c r="P46" s="352"/>
+      <c r="Q46" s="352"/>
+      <c r="R46" s="352"/>
+      <c r="S46" s="352"/>
+      <c r="T46" s="352"/>
+      <c r="U46" s="352"/>
+      <c r="V46" s="352"/>
+      <c r="W46" s="352"/>
+      <c r="X46" s="352"/>
+      <c r="Y46" s="352"/>
+      <c r="Z46" s="352"/>
+      <c r="AA46" s="352"/>
+      <c r="AB46" s="352"/>
+      <c r="AC46" s="352"/>
       <c r="AF46" s="123"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
@@ -10112,15 +10305,15 @@
       </c>
       <c r="AB50" s="12">
         <f t="shared" si="0"/>
-        <v>-2173263</v>
+        <v>516</v>
       </c>
       <c r="AC50" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2174229</v>
       </c>
       <c r="AE50" s="12">
         <f t="shared" si="0"/>
@@ -10240,15 +10433,15 @@
       </c>
       <c r="AB51" s="12">
         <f t="shared" si="2"/>
-        <v>-2137586</v>
+        <v>367</v>
       </c>
       <c r="AC51" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2138490</v>
       </c>
       <c r="AE51" s="12">
         <f t="shared" si="2"/>
@@ -10368,15 +10561,15 @@
       </c>
       <c r="AB52" s="12">
         <f t="shared" si="3"/>
-        <v>-2218585</v>
+        <v>262</v>
       </c>
       <c r="AC52" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="AD52" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2219111</v>
       </c>
       <c r="AE52" s="12">
         <f t="shared" si="3"/>
@@ -10496,15 +10689,15 @@
       </c>
       <c r="AB53" s="12">
         <f t="shared" si="4"/>
-        <v>-2225800</v>
+        <v>523</v>
       </c>
       <c r="AC53" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="AD53" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-2226532</v>
       </c>
       <c r="AE53" s="12">
         <f t="shared" si="4"/>
@@ -10624,15 +10817,15 @@
       </c>
       <c r="AB54" s="12">
         <f t="shared" si="5"/>
-        <v>-2145056</v>
+        <v>328</v>
       </c>
       <c r="AC54" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2145633</v>
       </c>
       <c r="AE54" s="12">
         <f t="shared" si="5"/>
@@ -10752,15 +10945,15 @@
       </c>
       <c r="AB55" s="12">
         <f t="shared" si="6"/>
-        <v>-2230014</v>
+        <v>93</v>
       </c>
       <c r="AC55" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2230179</v>
       </c>
       <c r="AE55" s="12">
         <f t="shared" si="6"/>
@@ -10880,15 +11073,15 @@
       </c>
       <c r="AB56" s="12">
         <f t="shared" si="7"/>
-        <v>-2286727</v>
+        <v>175</v>
       </c>
       <c r="AC56" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2287078</v>
       </c>
       <c r="AE56" s="12">
         <f t="shared" si="7"/>
@@ -11008,15 +11201,15 @@
       </c>
       <c r="AB57" s="12">
         <f t="shared" si="8"/>
-        <v>-2179269</v>
+        <v>560</v>
       </c>
       <c r="AC57" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-2180094</v>
       </c>
       <c r="AE57" s="12">
         <f t="shared" si="8"/>
@@ -11136,15 +11329,15 @@
       </c>
       <c r="AB58" s="12">
         <f t="shared" si="9"/>
-        <v>-2166370</v>
+        <v>194</v>
       </c>
       <c r="AC58" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2166745</v>
       </c>
       <c r="AE58" s="12">
         <f t="shared" si="9"/>
@@ -11264,15 +11457,15 @@
       </c>
       <c r="AB59" s="12">
         <f t="shared" si="10"/>
-        <v>-2230095</v>
+        <v>518</v>
       </c>
       <c r="AC59" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="AD59" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-2231172</v>
       </c>
       <c r="AE59" s="12">
         <f t="shared" si="10"/>
@@ -11392,15 +11585,15 @@
       </c>
       <c r="AB60" s="12">
         <f t="shared" si="11"/>
-        <v>-2264448</v>
+        <v>20</v>
       </c>
       <c r="AC60" s="12">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="AD60" s="12">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2264719</v>
       </c>
       <c r="AE60" s="12">
         <f t="shared" si="11"/>
@@ -11520,15 +11713,15 @@
       </c>
       <c r="AB61" s="12">
         <f t="shared" si="12"/>
-        <v>-2111383</v>
+        <v>202</v>
       </c>
       <c r="AC61" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="AD61" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-2112105</v>
       </c>
       <c r="AE61" s="12">
         <f t="shared" si="12"/>
@@ -11648,15 +11841,15 @@
       </c>
       <c r="AB62" s="12">
         <f t="shared" si="13"/>
-        <v>-2199230</v>
+        <v>192</v>
       </c>
       <c r="AC62" s="12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="AD62" s="12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-2199738</v>
       </c>
       <c r="AE62" s="12">
         <f t="shared" si="13"/>
@@ -11776,15 +11969,15 @@
       </c>
       <c r="AB63" s="12">
         <f t="shared" si="14"/>
-        <v>-2188310</v>
+        <v>560</v>
       </c>
       <c r="AC63" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="AD63" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2189386</v>
       </c>
       <c r="AE63" s="12">
         <f t="shared" si="14"/>
@@ -11904,15 +12097,15 @@
       </c>
       <c r="AB64" s="12">
         <f t="shared" si="15"/>
-        <v>-2260050</v>
+        <v>563</v>
       </c>
       <c r="AC64" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="AD64" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-2261108</v>
       </c>
       <c r="AE64" s="12">
         <f t="shared" si="15"/>
@@ -12032,15 +12225,15 @@
       </c>
       <c r="AB65" s="12">
         <f t="shared" si="16"/>
-        <v>-2241992</v>
+        <v>604</v>
       </c>
       <c r="AC65" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="AD65" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>-2243202</v>
       </c>
       <c r="AE65" s="12">
         <f t="shared" si="16"/>
@@ -12160,15 +12353,15 @@
       </c>
       <c r="AB66" s="12">
         <f t="shared" si="17"/>
-        <v>-2254637</v>
+        <v>520</v>
       </c>
       <c r="AC66" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="AD66" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-2255524</v>
       </c>
       <c r="AE66" s="12">
         <f t="shared" si="17"/>
@@ -12288,15 +12481,15 @@
       </c>
       <c r="AB67" s="12">
         <f t="shared" si="18"/>
-        <v>-2179842</v>
+        <v>254</v>
       </c>
       <c r="AC67" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="AD67" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>-2180274</v>
       </c>
       <c r="AE67" s="12">
         <f t="shared" si="18"/>
@@ -12416,15 +12609,15 @@
       </c>
       <c r="AB68" s="12">
         <f t="shared" si="19"/>
-        <v>-2209908</v>
+        <v>398</v>
       </c>
       <c r="AC68" s="12">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="AD68" s="12">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>-2210826</v>
       </c>
       <c r="AE68" s="12">
         <f t="shared" si="19"/>
@@ -12544,15 +12737,15 @@
       </c>
       <c r="AB69" s="12">
         <f t="shared" si="20"/>
-        <v>-2250302</v>
+        <v>193</v>
       </c>
       <c r="AC69" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="AD69" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-2251031</v>
       </c>
       <c r="AE69" s="12">
         <f t="shared" si="20"/>
@@ -12672,15 +12865,15 @@
       </c>
       <c r="AB70" s="12">
         <f t="shared" si="21"/>
-        <v>-2263413</v>
+        <v>250</v>
       </c>
       <c r="AC70" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="AD70" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>-2263924</v>
       </c>
       <c r="AE70" s="12">
         <f t="shared" si="21"/>
@@ -12800,15 +12993,15 @@
       </c>
       <c r="AB71" s="12">
         <f t="shared" si="22"/>
-        <v>-2250232</v>
+        <v>168</v>
       </c>
       <c r="AC71" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="AD71" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2250834</v>
       </c>
       <c r="AE71" s="12">
         <f t="shared" si="22"/>
@@ -12928,15 +13121,15 @@
       </c>
       <c r="AB72" s="12">
         <f t="shared" si="23"/>
-        <v>-2229254</v>
+        <v>433</v>
       </c>
       <c r="AC72" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="AD72" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-2229880</v>
       </c>
       <c r="AE72" s="12">
         <f t="shared" si="23"/>
@@ -13056,15 +13249,15 @@
       </c>
       <c r="AB73" s="12">
         <f t="shared" si="24"/>
-        <v>-2190501</v>
+        <v>239</v>
       </c>
       <c r="AC73" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="AD73" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-2190931</v>
       </c>
       <c r="AE73" s="12">
         <f t="shared" si="24"/>
@@ -13184,15 +13377,15 @@
       </c>
       <c r="AB74" s="12">
         <f t="shared" si="25"/>
-        <v>-2143911</v>
+        <v>280</v>
       </c>
       <c r="AC74" s="12">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="AD74" s="12">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>-2144443</v>
       </c>
       <c r="AE74" s="12">
         <f t="shared" si="25"/>
@@ -13312,15 +13505,15 @@
       </c>
       <c r="AB75" s="12">
         <f t="shared" si="26"/>
-        <v>-1901172</v>
+        <v>560</v>
       </c>
       <c r="AC75" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="AD75" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1902028</v>
       </c>
       <c r="AE75" s="12">
         <f t="shared" si="26"/>
@@ -13440,15 +13633,15 @@
       </c>
       <c r="AB76" s="12">
         <f t="shared" si="27"/>
-        <v>-2196430</v>
+        <v>250</v>
       </c>
       <c r="AC76" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="AD76" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>-2196898</v>
       </c>
       <c r="AE76" s="12">
         <f t="shared" si="27"/>
@@ -13568,15 +13761,15 @@
       </c>
       <c r="AB77" s="12">
         <f t="shared" si="28"/>
-        <v>-785567</v>
+        <v>296</v>
       </c>
       <c r="AC77" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="AD77" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-786255</v>
       </c>
       <c r="AE77" s="12">
         <f t="shared" si="28"/>
@@ -13696,15 +13889,15 @@
       </c>
       <c r="AB78" s="12">
         <f t="shared" si="29"/>
-        <v>-715627</v>
+        <v>364</v>
       </c>
       <c r="AC78" s="12">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="AD78" s="12">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-716511</v>
       </c>
       <c r="AE78" s="12">
         <f t="shared" si="29"/>
@@ -13824,15 +14017,15 @@
       </c>
       <c r="AB79" s="12">
         <f t="shared" si="30"/>
-        <v>-751907</v>
+        <v>441</v>
       </c>
       <c r="AC79" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="AD79" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-752586</v>
       </c>
       <c r="AE79" s="12">
         <f t="shared" si="30"/>
@@ -13952,15 +14145,15 @@
       </c>
       <c r="AB80" s="12">
         <f t="shared" si="31"/>
-        <v>-779481</v>
+        <v>432</v>
       </c>
       <c r="AC80" s="12">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="AD80" s="12">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-780280</v>
       </c>
       <c r="AE80" s="12">
         <f t="shared" si="31"/>
@@ -14080,15 +14273,15 @@
       </c>
       <c r="AB81" s="12">
         <f t="shared" si="32"/>
-        <v>-753957</v>
+        <v>521</v>
       </c>
       <c r="AC81" s="12">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="AD81" s="12">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-754996</v>
       </c>
       <c r="AE81" s="12">
         <f t="shared" si="32"/>
@@ -14208,15 +14401,15 @@
       </c>
       <c r="AB82" s="12">
         <f t="shared" si="33"/>
-        <v>-795972</v>
+        <v>365</v>
       </c>
       <c r="AC82" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="AD82" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>-796771</v>
       </c>
       <c r="AE82" s="12">
         <f t="shared" si="33"/>
@@ -14336,15 +14529,15 @@
       </c>
       <c r="AB83" s="12">
         <f t="shared" si="34"/>
-        <v>-441306</v>
+        <v>305</v>
       </c>
       <c r="AC83" s="12">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="AD83" s="12">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>-442171</v>
       </c>
       <c r="AE83" s="12">
         <f t="shared" si="34"/>
@@ -14464,15 +14657,15 @@
       </c>
       <c r="AB84" s="12">
         <f t="shared" si="35"/>
-        <v>-770439</v>
+        <v>561</v>
       </c>
       <c r="AC84" s="12">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="AD84" s="12">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-771221</v>
       </c>
       <c r="AE84" s="12">
         <f t="shared" si="35"/>
@@ -14592,15 +14785,15 @@
       </c>
       <c r="AB85" s="312">
         <f t="shared" ref="AB85" si="58">AB40-AA40</f>
-        <v>-8863</v>
+        <v>205</v>
       </c>
       <c r="AC85" s="312">
         <f>AC40-AB40</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AD85" s="312">
         <f t="shared" ref="AD85" si="59">AD40-AC40</f>
-        <v>0</v>
+        <v>-9408</v>
       </c>
       <c r="AE85" s="312">
         <f t="shared" ref="AE85" si="60">AE40-AD40</f>
@@ -14720,15 +14913,15 @@
       </c>
       <c r="AB86" s="312">
         <f t="shared" ref="AB86" si="84">AB41-AA41</f>
-        <v>-7178</v>
+        <v>239</v>
       </c>
       <c r="AC86" s="312">
         <f>AC41-AB41</f>
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AD86" s="312">
         <f t="shared" ref="AD86" si="85">AD41-AC41</f>
-        <v>0</v>
+        <v>-7591</v>
       </c>
       <c r="AE86" s="312">
         <f t="shared" ref="AE86" si="86">AE41-AD41</f>
@@ -14848,15 +15041,15 @@
       </c>
       <c r="AB87" s="312">
         <f>AB42-AA42</f>
-        <v>-31177</v>
+        <v>316</v>
       </c>
       <c r="AC87" s="312">
         <f>AC42-AB42</f>
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="AD87" s="312">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-31851</v>
       </c>
       <c r="AE87" s="312">
         <f t="shared" si="90"/>
@@ -14976,7 +15169,7 @@
       </c>
       <c r="AB88" s="312">
         <f t="shared" si="105"/>
-        <v>-2239</v>
+        <v>0</v>
       </c>
       <c r="AC88" s="312">
         <f>AC43-AB43</f>
@@ -14984,7 +15177,7 @@
       </c>
       <c r="AD88" s="312">
         <f t="shared" ref="AD88:AF89" si="106">AD43-AC43</f>
-        <v>0</v>
+        <v>-2239</v>
       </c>
       <c r="AE88" s="312">
         <f t="shared" si="106"/>
@@ -15104,7 +15297,7 @@
       </c>
       <c r="AB89" s="312">
         <f t="shared" si="105"/>
-        <v>-2123</v>
+        <v>0</v>
       </c>
       <c r="AC89" s="312">
         <f>AC44-AB44</f>
@@ -15112,7 +15305,7 @@
       </c>
       <c r="AD89" s="312">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>-2123</v>
       </c>
       <c r="AE89" s="312">
         <f t="shared" ref="AE89:AF89" si="114">AE44-AD44</f>
@@ -15234,15 +15427,15 @@
       </c>
       <c r="AB91" s="15">
         <f t="shared" si="115"/>
-        <v>-65173616</v>
+        <v>13267</v>
       </c>
       <c r="AC91" s="15">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>13234</v>
       </c>
       <c r="AD91" s="15">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>-65200117</v>
       </c>
       <c r="AE91" s="15">
         <f t="shared" si="115"/>
@@ -15403,14 +15596,14 @@
     </row>
     <row r="2" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
-      <c r="B2" s="358" t="s">
+      <c r="B2" s="360" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="358"/>
-      <c r="D2" s="359" t="s">
+      <c r="C2" s="360"/>
+      <c r="D2" s="361" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="359"/>
+      <c r="E2" s="361"/>
       <c r="F2" s="229" t="s">
         <v>163</v>
       </c>
@@ -15516,59 +15709,59 @@
     </row>
     <row r="3" spans="1:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="360" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="359" t="s">
+      <c r="C3" s="360"/>
+      <c r="D3" s="361" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="359"/>
-      <c r="F3" s="356" t="s">
+      <c r="E3" s="361"/>
+      <c r="F3" s="358" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="356" t="s">
+      <c r="G3" s="358" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="356" t="s">
+      <c r="H3" s="358" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="356" t="s">
+      <c r="I3" s="358" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="356" t="s">
+      <c r="J3" s="358" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="356" t="s">
+      <c r="K3" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="356" t="s">
+      <c r="L3" s="358" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="356" t="s">
+      <c r="M3" s="358" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="366" t="s">
+      <c r="N3" s="368" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="366" t="s">
+      <c r="O3" s="368" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="365"/>
-      <c r="Q3" s="367" t="s">
+      <c r="P3" s="367"/>
+      <c r="Q3" s="369" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="368"/>
-      <c r="S3" s="369"/>
-      <c r="T3" s="370" t="s">
+      <c r="R3" s="370"/>
+      <c r="S3" s="371"/>
+      <c r="T3" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="371"/>
-      <c r="V3" s="372"/>
-      <c r="W3" s="363" t="s">
+      <c r="U3" s="373"/>
+      <c r="V3" s="374"/>
+      <c r="W3" s="365" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="363" t="s">
+      <c r="X3" s="365" t="s">
         <v>162</v>
       </c>
       <c r="Y3" s="326" t="s">
@@ -15599,17 +15792,17 @@
       <c r="E4" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="356"/>
-      <c r="G4" s="357"/>
-      <c r="H4" s="357"/>
-      <c r="I4" s="356"/>
-      <c r="J4" s="356"/>
-      <c r="K4" s="356"/>
-      <c r="L4" s="356"/>
-      <c r="M4" s="356"/>
-      <c r="N4" s="366"/>
-      <c r="O4" s="366"/>
-      <c r="P4" s="365"/>
+      <c r="F4" s="358"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
+      <c r="I4" s="358"/>
+      <c r="J4" s="358"/>
+      <c r="K4" s="358"/>
+      <c r="L4" s="358"/>
+      <c r="M4" s="358"/>
+      <c r="N4" s="368"/>
+      <c r="O4" s="368"/>
+      <c r="P4" s="367"/>
       <c r="Q4" s="192" t="s">
         <v>140</v>
       </c>
@@ -15628,8 +15821,8 @@
       <c r="V4" s="233" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="364"/>
+      <c r="W4" s="366"/>
+      <c r="X4" s="366"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="59">
@@ -15701,7 +15894,7 @@
       </c>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="360" t="s">
+      <c r="A6" s="362" t="s">
         <v>192</v>
       </c>
       <c r="B6" s="289">
@@ -15770,7 +15963,7 @@
       </c>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="360"/>
+      <c r="A7" s="362"/>
       <c r="B7" s="289">
         <v>33</v>
       </c>
@@ -15837,7 +16030,7 @@
       </c>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="360"/>
+      <c r="A8" s="362"/>
       <c r="B8" s="289">
         <v>30</v>
       </c>
@@ -15902,7 +16095,7 @@
       </c>
     </row>
     <row r="9" spans="1:38" s="123" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="360"/>
+      <c r="A9" s="362"/>
       <c r="B9" s="289">
         <v>0</v>
       </c>
@@ -15967,7 +16160,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="360"/>
+      <c r="A10" s="362"/>
       <c r="B10" s="289">
         <v>3</v>
       </c>
@@ -27470,11 +27663,11 @@
         <f>A173+1</f>
         <v>46321</v>
       </c>
-      <c r="B180" s="124">
-        <v>38</v>
-      </c>
-      <c r="C180" s="124">
-        <v>41</v>
+      <c r="B180" s="289">
+        <v>36</v>
+      </c>
+      <c r="C180" s="289">
+        <v>43</v>
       </c>
       <c r="D180" s="146">
         <f>'Data Ocupacion'!BB31</f>
@@ -27493,7 +27686,7 @@
       </c>
       <c r="H180" s="124">
         <f t="shared" ref="H180:H185" si="151">B180+C180*2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I180" s="124">
         <f t="shared" ref="I180:I185" si="152">D180+E180</f>
@@ -27532,7 +27725,7 @@
       </c>
       <c r="X180" s="180">
         <f>H180*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5261.8600000000006</v>
       </c>
       <c r="Z180" s="123"/>
       <c r="AA180" s="123"/>
@@ -27542,11 +27735,11 @@
     </row>
     <row r="181" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="270"/>
-      <c r="B181" s="124">
-        <v>36</v>
-      </c>
-      <c r="C181" s="124">
-        <v>42</v>
+      <c r="B181" s="289">
+        <v>33</v>
+      </c>
+      <c r="C181" s="289">
+        <v>45</v>
       </c>
       <c r="D181" s="146">
         <f>'Data Ocupacion'!BB32</f>
@@ -27565,7 +27758,7 @@
       </c>
       <c r="H181" s="124">
         <f t="shared" si="151"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I181" s="124">
         <f t="shared" si="152"/>
@@ -27604,7 +27797,7 @@
       </c>
       <c r="X181" s="180">
         <f>H181*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5304.9900000000007</v>
       </c>
       <c r="Z181" s="123"/>
       <c r="AA181" s="123"/>
@@ -27614,11 +27807,11 @@
     </row>
     <row r="182" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A182" s="270"/>
-      <c r="B182" s="124">
-        <v>34</v>
-      </c>
-      <c r="C182" s="124">
-        <v>1</v>
+      <c r="B182" s="289">
+        <v>33</v>
+      </c>
+      <c r="C182" s="289">
+        <v>2</v>
       </c>
       <c r="D182" s="125">
         <f>'Data Ocupacion'!BB33</f>
@@ -27637,7 +27830,7 @@
       </c>
       <c r="H182" s="124">
         <f t="shared" si="151"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I182" s="124">
         <f t="shared" si="152"/>
@@ -27676,16 +27869,16 @@
       </c>
       <c r="X182" s="180">
         <f>H182*$M$1</f>
-        <v>1047.96</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="183" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="270"/>
-      <c r="B183" s="124">
-        <v>31</v>
-      </c>
-      <c r="C183" s="124">
-        <v>1</v>
+      <c r="B183" s="289">
+        <v>30</v>
+      </c>
+      <c r="C183" s="289">
+        <v>2</v>
       </c>
       <c r="D183" s="125">
         <f>'Data Ocupacion'!BB34</f>
@@ -27704,7 +27897,7 @@
       </c>
       <c r="H183" s="124">
         <f t="shared" si="151"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I183" s="124">
         <f t="shared" si="152"/>
@@ -27741,15 +27934,15 @@
       </c>
       <c r="X183" s="180">
         <f>H183*$M$1</f>
-        <v>960.63</v>
+        <v>989.74</v>
       </c>
     </row>
     <row r="184" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="270"/>
-      <c r="B184" s="124">
-        <v>0</v>
-      </c>
-      <c r="C184" s="124">
+      <c r="B184" s="289">
+        <v>0</v>
+      </c>
+      <c r="C184" s="289">
         <v>0</v>
       </c>
       <c r="D184" s="125">
@@ -27811,10 +28004,10 @@
     </row>
     <row r="185" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="270"/>
-      <c r="B185" s="124">
+      <c r="B185" s="289">
         <v>3</v>
       </c>
-      <c r="C185" s="124">
+      <c r="C185" s="289">
         <v>0</v>
       </c>
       <c r="D185" s="249">
@@ -27878,11 +28071,11 @@
       <c r="A186" s="19"/>
       <c r="B186" s="118">
         <f>SUM(B180:B185)</f>
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C186" s="118">
         <f>SUM(C180:C185)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D186" s="319">
         <f>SUM(D180:D185)</f>
@@ -27899,7 +28092,7 @@
       </c>
       <c r="H186" s="118">
         <f t="shared" si="155"/>
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I186" s="118">
         <f t="shared" si="155"/>
@@ -27942,7 +28135,7 @@
       </c>
       <c r="X186" s="191">
         <f>SUM(X180:X185)</f>
-        <v>12435.99</v>
+        <v>12709.860000000002</v>
       </c>
     </row>
     <row r="187" spans="1:30" x14ac:dyDescent="0.25">
@@ -27950,55 +28143,57 @@
         <f>A180+1</f>
         <v>46322</v>
       </c>
-      <c r="B187" s="124">
-        <v>38</v>
-      </c>
-      <c r="C187" s="124">
-        <v>41</v>
-      </c>
-      <c r="D187" s="137">
+      <c r="B187" s="289">
+        <v>36</v>
+      </c>
+      <c r="C187" s="289">
+        <v>43</v>
+      </c>
+      <c r="D187" s="125">
         <f>'Data Ocupacion'!BD31</f>
-        <v>0</v>
-      </c>
-      <c r="E187" s="137">
+        <v>36</v>
+      </c>
+      <c r="E187" s="125">
         <f>'Data Ocupacion'!BE31</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F187" s="217" t="s">
         <v>38</v>
       </c>
       <c r="G187" s="218">
         <f t="shared" ref="G187:G192" si="156">D187+E187*2</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H187" s="124">
         <f t="shared" ref="H187:H192" si="157">B187+C187*2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I187" s="219">
         <f t="shared" ref="I187:I192" si="158">D187+E187</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J187" s="124">
         <f>G187*M$2</f>
-        <v>0</v>
+        <v>5261.8600000000006</v>
       </c>
       <c r="K187" s="152">
         <f>I187*M$2</f>
-        <v>0</v>
+        <v>3407.27</v>
       </c>
       <c r="L187" s="124">
         <f t="shared" ref="L187:L192" si="159">J187*104</f>
-        <v>0</v>
+        <v>547233.44000000006</v>
       </c>
       <c r="M187" s="124">
         <f t="shared" ref="M187:M192" si="160">I187*104</f>
-        <v>0</v>
+        <v>8216</v>
       </c>
       <c r="N187" s="18"/>
       <c r="O187" s="18"/>
       <c r="P187" s="145"/>
-      <c r="Q187" s="181"/>
+      <c r="Q187" s="181">
+        <v>1</v>
+      </c>
       <c r="R187" s="181"/>
       <c r="S187" s="203"/>
       <c r="T187" s="279"/>
@@ -28006,59 +28201,59 @@
       <c r="V187" s="225"/>
       <c r="W187" s="180">
         <f>J187-(Q187*($M$2-$K$1))-(R187*($M$2-$M$1))- (S187*($M$2-$I$2))+ (T187*($G$2))</f>
-        <v>0</v>
+        <v>5244.130000000001</v>
       </c>
       <c r="X187" s="180">
         <f>H187*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5261.8600000000006</v>
       </c>
     </row>
     <row r="188" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="270"/>
-      <c r="B188" s="124">
-        <v>36</v>
-      </c>
-      <c r="C188" s="124">
-        <v>42</v>
+      <c r="B188" s="289">
+        <v>33</v>
+      </c>
+      <c r="C188" s="289">
+        <v>45</v>
       </c>
       <c r="D188" s="137">
         <f>'Data Ocupacion'!BD32</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E188" s="125">
         <f>'Data Ocupacion'!BE32</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F188" s="217" t="s">
         <v>52</v>
       </c>
       <c r="G188" s="218">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H188" s="124">
         <f t="shared" si="157"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I188" s="124">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J188" s="124">
         <f>G188*M$2</f>
-        <v>0</v>
+        <v>5261.8600000000006</v>
       </c>
       <c r="K188" s="152">
         <f>I188*M$2</f>
-        <v>0</v>
+        <v>3364.1400000000003</v>
       </c>
       <c r="L188" s="124">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>547233.44000000006</v>
       </c>
       <c r="M188" s="124">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>8112</v>
       </c>
       <c r="N188" s="18"/>
       <c r="O188" s="18"/>
@@ -28066,69 +28261,73 @@
       <c r="Q188" s="184"/>
       <c r="R188" s="184"/>
       <c r="S188" s="214"/>
-      <c r="T188" s="181"/>
+      <c r="T188" s="181">
+        <v>3</v>
+      </c>
       <c r="U188" s="214"/>
       <c r="V188" s="226"/>
       <c r="W188" s="183">
         <f>J188-(T188*($M$2-$K$1)+(U188*($M$2-$M$1)))</f>
-        <v>0</v>
+        <v>5208.670000000001</v>
       </c>
       <c r="X188" s="180">
         <f>H188*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5304.9900000000007</v>
       </c>
     </row>
     <row r="189" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="270"/>
-      <c r="B189" s="124">
-        <v>34</v>
-      </c>
-      <c r="C189" s="124">
-        <v>1</v>
+      <c r="B189" s="289">
+        <v>33</v>
+      </c>
+      <c r="C189" s="289">
+        <v>2</v>
       </c>
       <c r="D189" s="125">
         <f>'Data Ocupacion'!BD33</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E189" s="125">
         <f>'Data Ocupacion'!BE33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" s="217" t="s">
         <v>36</v>
       </c>
       <c r="G189" s="218">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H189" s="124">
         <f t="shared" si="157"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I189" s="124">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J189" s="124">
         <f>G189*M$1</f>
-        <v>0</v>
+        <v>1047.96</v>
       </c>
       <c r="K189" s="152">
         <f>I189*M$1</f>
-        <v>0</v>
+        <v>1018.85</v>
       </c>
       <c r="L189" s="124">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>108987.84</v>
       </c>
       <c r="M189" s="124">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="N189" s="18"/>
       <c r="O189" s="18"/>
       <c r="P189" s="145"/>
-      <c r="Q189" s="239"/>
+      <c r="Q189" s="239">
+        <v>1</v>
+      </c>
       <c r="R189" s="188"/>
       <c r="S189" s="225"/>
       <c r="T189" s="184"/>
@@ -28136,59 +28335,59 @@
       <c r="V189" s="187"/>
       <c r="W189" s="180">
         <f>J189-(Q189*($M$1-$K$1))</f>
-        <v>0</v>
+        <v>1044.25</v>
       </c>
       <c r="X189" s="180">
         <f>H189*$M$1</f>
-        <v>1047.96</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="190" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="270"/>
-      <c r="B190" s="124">
-        <v>31</v>
-      </c>
-      <c r="C190" s="124">
-        <v>1</v>
+      <c r="B190" s="289">
+        <v>30</v>
+      </c>
+      <c r="C190" s="289">
+        <v>2</v>
       </c>
       <c r="D190" s="125">
         <f>'Data Ocupacion'!BD34</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E190" s="125">
         <f>'Data Ocupacion'!BE34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="217" t="s">
         <v>53</v>
       </c>
       <c r="G190" s="218">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H190" s="124">
         <f t="shared" si="157"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I190" s="124">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J190" s="124">
         <f>G190*M$1</f>
-        <v>0</v>
+        <v>960.63</v>
       </c>
       <c r="K190" s="152">
         <f>I190*M$1</f>
-        <v>0</v>
+        <v>931.52</v>
       </c>
       <c r="L190" s="124">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>99905.52</v>
       </c>
       <c r="M190" s="124">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>3328</v>
       </c>
       <c r="N190" s="18"/>
       <c r="O190" s="18"/>
@@ -28201,19 +28400,19 @@
       <c r="V190" s="187"/>
       <c r="W190" s="180">
         <f>J190</f>
-        <v>0</v>
+        <v>960.63</v>
       </c>
       <c r="X190" s="180">
         <f>H190*$M$1</f>
-        <v>960.63</v>
+        <v>989.74</v>
       </c>
     </row>
     <row r="191" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="270"/>
-      <c r="B191" s="124">
-        <v>0</v>
-      </c>
-      <c r="C191" s="124">
+      <c r="B191" s="289">
+        <v>0</v>
+      </c>
+      <c r="C191" s="289">
         <v>0</v>
       </c>
       <c r="D191" s="125">
@@ -28275,15 +28474,15 @@
     </row>
     <row r="192" spans="1:30" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="270"/>
-      <c r="B192" s="124">
+      <c r="B192" s="289">
         <v>3</v>
       </c>
-      <c r="C192" s="124">
+      <c r="C192" s="289">
         <v>0</v>
       </c>
       <c r="D192" s="249">
         <f>'Data Ocupacion'!BD36</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E192" s="125">
         <f>'Data Ocupacion'!BE36</f>
@@ -28294,7 +28493,7 @@
       </c>
       <c r="G192" s="218">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H192" s="124">
         <f t="shared" si="157"/>
@@ -28302,23 +28501,23 @@
       </c>
       <c r="I192" s="221">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J192" s="124">
         <f>G192*K$1</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="K192" s="152">
         <f>I192*K$1</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="L192" s="124">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>7924.7999999999993</v>
       </c>
       <c r="M192" s="124">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="N192" s="18"/>
       <c r="O192" s="18"/>
@@ -28331,7 +28530,7 @@
       <c r="V192" s="187"/>
       <c r="W192" s="180">
         <f>J192</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="X192" s="180">
         <f>H192*$K$1</f>
@@ -28342,56 +28541,56 @@
       <c r="A193" s="19"/>
       <c r="B193" s="118">
         <f>SUM(B187:B192)</f>
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C193" s="118">
         <f>SUM(C187:C192)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D193" s="147">
         <f>SUM(D187:D192)</f>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E193" s="147">
         <f>SUM(E187:E192)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F193" s="118"/>
       <c r="G193" s="118">
         <f t="shared" ref="G193:M193" si="161">SUM(G187:G192)</f>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="H193" s="118">
         <f t="shared" si="161"/>
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I193" s="118">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="J193" s="119">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>12608.51</v>
       </c>
       <c r="K193" s="118">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>8797.9800000000014</v>
       </c>
       <c r="L193" s="118">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>1311285.0400000003</v>
       </c>
       <c r="M193" s="118">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>23608</v>
       </c>
       <c r="N193" s="122">
         <f>'Odometro-Kilometraje'!AB91</f>
-        <v>-65173616</v>
+        <v>13267</v>
       </c>
       <c r="O193" s="20">
         <f>(W193/N193)*100</f>
-        <v>0</v>
+        <v>94.474108690736429</v>
       </c>
       <c r="P193" s="190"/>
       <c r="Q193" s="179"/>
@@ -28402,11 +28601,11 @@
       <c r="V193" s="179"/>
       <c r="W193" s="191">
         <f>SUM(W187:W192)</f>
-        <v>0</v>
+        <v>12533.880000000003</v>
       </c>
       <c r="X193" s="191">
         <f>SUM(X187:X192)</f>
-        <v>12435.99</v>
+        <v>12709.860000000002</v>
       </c>
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.25">
@@ -28415,54 +28614,56 @@
         <v>46323</v>
       </c>
       <c r="B194" s="289">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C194" s="289">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D194" s="125">
         <f>'Data Ocupacion'!BF31</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E194" s="125">
         <f>'Data Ocupacion'!BG31</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F194" s="217" t="s">
         <v>38</v>
       </c>
       <c r="G194" s="218">
         <f t="shared" ref="G194:G199" si="162">D194+E194*2</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H194" s="124">
         <f t="shared" ref="H194:H199" si="163">B194+C194*2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I194" s="219">
         <f t="shared" ref="I194:I199" si="164">D194+E194</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J194" s="219">
         <f>G194*M$2</f>
-        <v>0</v>
+        <v>5261.8600000000006</v>
       </c>
       <c r="K194" s="152">
         <f>I194*M$2</f>
-        <v>0</v>
+        <v>3407.27</v>
       </c>
       <c r="L194" s="124">
         <f t="shared" ref="L194:L199" si="165">J194*104</f>
-        <v>0</v>
+        <v>547233.44000000006</v>
       </c>
       <c r="M194" s="124">
         <f t="shared" ref="M194:M199" si="166">I194*104</f>
-        <v>0</v>
+        <v>8216</v>
       </c>
       <c r="N194" s="18"/>
       <c r="O194" s="18"/>
       <c r="P194" s="145"/>
-      <c r="Q194" s="181"/>
+      <c r="Q194" s="181">
+        <v>1</v>
+      </c>
       <c r="R194" s="181"/>
       <c r="S194" s="203"/>
       <c r="T194" s="279"/>
@@ -28470,59 +28671,59 @@
       <c r="V194" s="225"/>
       <c r="W194" s="180">
         <f>J194-(Q194*($M$2-$K$1))-(R194*($M$2-$M$1))- (S194*($M$2-$I$2))+ (T194*($G$2))</f>
-        <v>0</v>
+        <v>5244.130000000001</v>
       </c>
       <c r="X194" s="180">
         <f>H194*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5261.8600000000006</v>
       </c>
     </row>
     <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="199"/>
       <c r="B195" s="289">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C195" s="289">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D195" s="125">
         <f>'Data Ocupacion'!BF32</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E195" s="125">
         <f>'Data Ocupacion'!BG32</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F195" s="217" t="s">
         <v>52</v>
       </c>
       <c r="G195" s="218">
         <f t="shared" si="162"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H195" s="124">
         <f t="shared" si="163"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I195" s="124">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J195" s="124">
         <f>G195*M$2</f>
-        <v>0</v>
+        <v>5261.8600000000006</v>
       </c>
       <c r="K195" s="152">
         <f>I195*M$2</f>
-        <v>0</v>
+        <v>3364.1400000000003</v>
       </c>
       <c r="L195" s="124">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>547233.44000000006</v>
       </c>
       <c r="M195" s="124">
         <f t="shared" si="166"/>
-        <v>0</v>
+        <v>8112</v>
       </c>
       <c r="N195" s="18"/>
       <c r="O195" s="18"/>
@@ -28530,71 +28731,75 @@
       <c r="Q195" s="184"/>
       <c r="R195" s="184"/>
       <c r="S195" s="214"/>
-      <c r="T195" s="181"/>
+      <c r="T195" s="181">
+        <v>4</v>
+      </c>
       <c r="U195" s="214"/>
       <c r="V195" s="226"/>
       <c r="W195" s="183">
         <f>J195-(T195*($M$2-$K$1)+(U195*($M$2-$M$1)))</f>
-        <v>0</v>
+        <v>5190.9400000000005</v>
       </c>
       <c r="X195" s="180">
         <f>H195*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5304.9900000000007</v>
       </c>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="199"/>
       <c r="B196" s="289">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C196" s="289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D196" s="125">
         <f>'Data Ocupacion'!BF33</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E196" s="125">
         <f>'Data Ocupacion'!BG33</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F196" s="217" t="s">
         <v>36</v>
       </c>
       <c r="G196" s="218">
         <f t="shared" si="162"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H196" s="124">
         <f t="shared" si="163"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I196" s="124">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J196" s="124">
         <f>G196*M$1</f>
-        <v>0</v>
+        <v>1077.07</v>
       </c>
       <c r="K196" s="152">
         <f>I196*M$1</f>
-        <v>0</v>
+        <v>1018.85</v>
       </c>
       <c r="L196" s="124">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>112015.28</v>
       </c>
       <c r="M196" s="124">
         <f t="shared" si="166"/>
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="N196" s="18"/>
       <c r="O196" s="18" t="s">
         <v>144</v>
       </c>
       <c r="P196" s="145"/>
-      <c r="Q196" s="239"/>
+      <c r="Q196" s="239">
+        <v>2</v>
+      </c>
       <c r="R196" s="188"/>
       <c r="S196" s="225"/>
       <c r="T196" s="184"/>
@@ -28602,59 +28807,59 @@
       <c r="V196" s="187"/>
       <c r="W196" s="180">
         <f>J196-(Q196*($M$1-$K$1))</f>
-        <v>0</v>
+        <v>1069.6499999999999</v>
       </c>
       <c r="X196" s="180">
         <f>H196*$M$1</f>
-        <v>1047.96</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="197" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="199"/>
       <c r="B197" s="289">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C197" s="289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D197" s="125">
         <f>'Data Ocupacion'!BF34</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E197" s="125">
         <f>'Data Ocupacion'!BG34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F197" s="217" t="s">
         <v>53</v>
       </c>
       <c r="G197" s="218">
         <f t="shared" si="162"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H197" s="124">
         <f t="shared" si="163"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I197" s="124">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J197" s="124">
         <f>G197*M$1</f>
-        <v>0</v>
+        <v>989.74</v>
       </c>
       <c r="K197" s="152">
         <f>I197*M$1</f>
-        <v>0</v>
+        <v>931.52</v>
       </c>
       <c r="L197" s="124">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>102932.96</v>
       </c>
       <c r="M197" s="124">
         <f t="shared" si="166"/>
-        <v>0</v>
+        <v>3328</v>
       </c>
       <c r="N197" s="18"/>
       <c r="O197" s="18" t="s">
@@ -28669,11 +28874,11 @@
       <c r="V197" s="187"/>
       <c r="W197" s="180">
         <f>J197</f>
-        <v>0</v>
+        <v>989.74</v>
       </c>
       <c r="X197" s="180">
         <f>H197*$M$1</f>
-        <v>960.63</v>
+        <v>989.74</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28751,7 +28956,7 @@
       </c>
       <c r="D199" s="249">
         <f>'Data Ocupacion'!BF36</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E199" s="125">
         <f>'Data Ocupacion'!BG36</f>
@@ -28762,7 +28967,7 @@
       </c>
       <c r="G199" s="218">
         <f t="shared" si="162"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H199" s="124">
         <f t="shared" si="163"/>
@@ -28770,23 +28975,23 @@
       </c>
       <c r="I199" s="221">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J199" s="221">
         <f>G199*K$1</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="K199" s="152">
         <f>I199*K$1</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="L199" s="124">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>7924.7999999999993</v>
       </c>
       <c r="M199" s="124">
         <f t="shared" si="166"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="N199" s="18"/>
       <c r="O199" s="18"/>
@@ -28799,7 +29004,7 @@
       <c r="V199" s="187"/>
       <c r="W199" s="180">
         <f>J199</f>
-        <v>0</v>
+        <v>76.199999999999989</v>
       </c>
       <c r="X199" s="180">
         <f>H199*$K$1</f>
@@ -28810,56 +29015,56 @@
       <c r="A200" s="19"/>
       <c r="B200" s="118">
         <f>SUM(B194:B199)</f>
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C200" s="118">
         <f>SUM(C194:C199)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D200" s="147">
         <f>SUM(D194:D199)</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E200" s="147">
         <f>SUM(E194:E199)</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F200" s="118"/>
       <c r="G200" s="118">
         <f t="shared" ref="G200:M200" si="167">SUM(G194:G199)</f>
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="H200" s="118">
         <f t="shared" si="167"/>
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I200" s="118">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="J200" s="119">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>12666.730000000001</v>
       </c>
       <c r="K200" s="118">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>8797.9800000000014</v>
       </c>
       <c r="L200" s="118">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>1317339.9200000002</v>
       </c>
       <c r="M200" s="118">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>23608</v>
       </c>
       <c r="N200" s="122">
         <f>'Odometro-Kilometraje'!AC91</f>
-        <v>0</v>
-      </c>
-      <c r="O200" s="20" t="e">
+        <v>13234</v>
+      </c>
+      <c r="O200" s="20">
         <f>(W200/N200)*100</f>
-        <v>#DIV/0!</v>
+        <v>94.987607677195115</v>
       </c>
       <c r="P200" s="190"/>
       <c r="Q200" s="179"/>
@@ -28870,11 +29075,11 @@
       <c r="V200" s="179"/>
       <c r="W200" s="191">
         <f>SUM(W194:W199)</f>
-        <v>0</v>
+        <v>12570.660000000002</v>
       </c>
       <c r="X200" s="191">
         <f>SUM(X194:X199)</f>
-        <v>12435.99</v>
+        <v>12709.860000000002</v>
       </c>
     </row>
     <row r="201" spans="1:25" x14ac:dyDescent="0.25">
@@ -28882,11 +29087,11 @@
         <f>A194+1</f>
         <v>46324</v>
       </c>
-      <c r="B201" s="124">
-        <v>38</v>
-      </c>
-      <c r="C201" s="124">
-        <v>41</v>
+      <c r="B201" s="289">
+        <v>36</v>
+      </c>
+      <c r="C201" s="289">
+        <v>43</v>
       </c>
       <c r="D201" s="146">
         <f>'Data Ocupacion'!BH31</f>
@@ -28905,7 +29110,7 @@
       </c>
       <c r="H201" s="124">
         <f t="shared" ref="H201:H206" si="169">B201+C201*2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I201" s="124">
         <f t="shared" ref="I201:I206" si="170">D201+E201</f>
@@ -28942,16 +29147,16 @@
       </c>
       <c r="X201" s="180">
         <f>H201*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5261.8600000000006</v>
       </c>
     </row>
     <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" s="199"/>
-      <c r="B202" s="124">
-        <v>36</v>
-      </c>
-      <c r="C202" s="124">
-        <v>42</v>
+      <c r="B202" s="289">
+        <v>33</v>
+      </c>
+      <c r="C202" s="289">
+        <v>45</v>
       </c>
       <c r="D202" s="146">
         <f>'Data Ocupacion'!BH32</f>
@@ -28970,7 +29175,7 @@
       </c>
       <c r="H202" s="124">
         <f t="shared" si="169"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I202" s="124">
         <f t="shared" si="170"/>
@@ -29007,16 +29212,16 @@
       </c>
       <c r="X202" s="180">
         <f>H202*$M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5304.9900000000007</v>
       </c>
     </row>
     <row r="203" spans="1:25" s="123" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="199"/>
-      <c r="B203" s="124">
-        <v>34</v>
-      </c>
-      <c r="C203" s="124">
-        <v>1</v>
+      <c r="B203" s="289">
+        <v>33</v>
+      </c>
+      <c r="C203" s="289">
+        <v>2</v>
       </c>
       <c r="D203" s="125">
         <f>'Data Ocupacion'!BH33</f>
@@ -29035,7 +29240,7 @@
       </c>
       <c r="H203" s="124">
         <f t="shared" si="169"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I203" s="124">
         <f t="shared" si="170"/>
@@ -29072,16 +29277,16 @@
       </c>
       <c r="X203" s="180">
         <f>H203*$M$1</f>
-        <v>1047.96</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="204" spans="1:25" s="123" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="199"/>
-      <c r="B204" s="124">
-        <v>31</v>
-      </c>
-      <c r="C204" s="124">
-        <v>1</v>
+      <c r="B204" s="289">
+        <v>30</v>
+      </c>
+      <c r="C204" s="289">
+        <v>2</v>
       </c>
       <c r="D204" s="125">
         <f>'Data Ocupacion'!BH34</f>
@@ -29100,7 +29305,7 @@
       </c>
       <c r="H204" s="124">
         <f t="shared" si="169"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I204" s="124">
         <f t="shared" si="170"/>
@@ -29137,15 +29342,15 @@
       </c>
       <c r="X204" s="180">
         <f>H204*$M$1</f>
-        <v>960.63</v>
+        <v>989.74</v>
       </c>
     </row>
     <row r="205" spans="1:25" s="123" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="199"/>
-      <c r="B205" s="124">
-        <v>0</v>
-      </c>
-      <c r="C205" s="124">
+      <c r="B205" s="289">
+        <v>0</v>
+      </c>
+      <c r="C205" s="289">
         <v>0</v>
       </c>
       <c r="D205" s="125">
@@ -29207,10 +29412,10 @@
     </row>
     <row r="206" spans="1:25" s="123" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="340"/>
-      <c r="B206" s="124">
+      <c r="B206" s="289">
         <v>3</v>
       </c>
-      <c r="C206" s="124">
+      <c r="C206" s="289">
         <v>0</v>
       </c>
       <c r="D206" s="125">
@@ -29274,11 +29479,11 @@
       <c r="A207" s="118"/>
       <c r="B207" s="118">
         <f>SUM(B201:B206)</f>
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C207" s="118">
         <f>SUM(C201:C206)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D207" s="147">
         <f>SUM(D201:D206)</f>
@@ -29295,7 +29500,7 @@
       </c>
       <c r="H207" s="118">
         <f t="shared" si="173"/>
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I207" s="118">
         <f t="shared" si="173"/>
@@ -29319,11 +29524,11 @@
       </c>
       <c r="N207" s="122">
         <f>'Odometro-Kilometraje'!AD91</f>
-        <v>0</v>
-      </c>
-      <c r="O207" s="20" t="e">
+        <v>-65200117</v>
+      </c>
+      <c r="O207" s="20">
         <f>(W207/N207)*100</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="P207" s="190"/>
       <c r="Q207" s="179"/>
@@ -29338,7 +29543,7 @@
       </c>
       <c r="X207" s="191">
         <f>SUM(X201:X206)</f>
-        <v>12435.99</v>
+        <v>12709.860000000002</v>
       </c>
       <c r="Y207" s="238"/>
     </row>
@@ -30241,38 +30446,38 @@
     <row r="222" spans="1:28" s="123" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="123" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="353" t="s">
+      <c r="B223" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="354"/>
-      <c r="D223" s="354"/>
-      <c r="E223" s="354"/>
-      <c r="F223" s="354"/>
-      <c r="G223" s="355"/>
+      <c r="C223" s="356"/>
+      <c r="D223" s="356"/>
+      <c r="E223" s="356"/>
+      <c r="F223" s="356"/>
+      <c r="G223" s="357"/>
       <c r="H223" s="284"/>
-      <c r="I223" s="353" t="s">
+      <c r="I223" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="354"/>
-      <c r="K223" s="354"/>
-      <c r="L223" s="354"/>
-      <c r="M223" s="354"/>
-      <c r="N223" s="355"/>
-      <c r="P223" s="373" t="s">
+      <c r="J223" s="356"/>
+      <c r="K223" s="356"/>
+      <c r="L223" s="356"/>
+      <c r="M223" s="356"/>
+      <c r="N223" s="357"/>
+      <c r="P223" s="375" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="373"/>
-      <c r="R223" s="373"/>
-      <c r="S223" s="374"/>
-      <c r="T223" s="370" t="s">
+      <c r="Q223" s="375"/>
+      <c r="R223" s="375"/>
+      <c r="S223" s="376"/>
+      <c r="T223" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="371"/>
-      <c r="V223" s="372"/>
-      <c r="W223" s="361" t="s">
+      <c r="U223" s="373"/>
+      <c r="V223" s="374"/>
+      <c r="W223" s="363" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="361" t="s">
+      <c r="X223" s="363" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30338,8 +30543,8 @@
       <c r="V224" s="224" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="362"/>
-      <c r="X224" s="362"/>
+      <c r="W224" s="364"/>
+      <c r="X224" s="364"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="22" t="s">
@@ -30347,11 +30552,11 @@
       </c>
       <c r="B225" s="113">
         <f t="shared" ref="B225:C227" si="186">B5+B12+B19+B26+B33+B40+B47+B54+B61+B68+B75+B82+B89+B96+B103+B110+B117+B124+B131+B138+B145+B152+B159+B166+B173+B180+B187+B194+B201+B208+B215</f>
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="C225" s="113">
         <f t="shared" si="186"/>
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="D225" s="113">
         <f t="shared" ref="D225:D230" si="187">B225+C225</f>
@@ -30363,11 +30568,11 @@
       </c>
       <c r="F225" s="138">
         <f>B225*43.13+C225*86.26</f>
-        <v>137757.22000000003</v>
+        <v>138102.26</v>
       </c>
       <c r="G225" s="138">
         <f t="shared" ref="G225:G230" si="188">F225*104</f>
-        <v>14326750.880000003</v>
+        <v>14362635.040000001</v>
       </c>
       <c r="H225" s="138"/>
       <c r="I225" s="113" t="e">
@@ -30397,7 +30602,7 @@
       <c r="O225" s="123"/>
       <c r="P225" s="206">
         <f>SUM(Q194,Q187,Q180,Q173,Q166,Q159,Q152,Q145,Q138,Q131,Q124,Q117,Q110,Q103,Q96,Q89,Q82,Q75,Q68,Q61,Q54,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q201,Q208,Q215)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q225" s="206">
         <f>SUM(R194,R187,R180,R173,R166,R159,R152,R145,R138,R131,R124,R117,R110,R103,R96,R89,R82,R75,R68,R61,R54,R47,R40,R33,R26,R19,R12,R5,R201,R208,R215)</f>
@@ -30413,7 +30618,7 @@
       </c>
       <c r="T225" s="206">
         <f>SUM(T194,T187,T180,T173,T166,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T201,T208,T215)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T167+T174+T181+T188+T195+T202+T209+T216</f>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="U225" s="206">
         <f>SUM(U194,U187,U180,U173,U166,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U201,U208,U216)</f>
@@ -30425,11 +30630,11 @@
       </c>
       <c r="W225" s="228">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>262336.77</v>
+        <v>287441.31</v>
       </c>
       <c r="X225" s="228">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
-        <v>315999.81000000011</v>
+        <v>317095.2900000001</v>
       </c>
     </row>
     <row r="226" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -30438,11 +30643,11 @@
       </c>
       <c r="B226" s="113">
         <f t="shared" si="186"/>
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="C226" s="113">
         <f t="shared" si="186"/>
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D226" s="113">
         <f t="shared" si="187"/>
@@ -30454,11 +30659,11 @@
       </c>
       <c r="F226" s="138">
         <f>B226*43.13+C226*86.26</f>
-        <v>138447.29999999999</v>
+        <v>138964.85999999999</v>
       </c>
       <c r="G226" s="138">
         <f t="shared" si="188"/>
-        <v>14398519.199999999</v>
+        <v>14452345.439999998</v>
       </c>
       <c r="H226" s="138"/>
       <c r="I226" s="113" t="e">
@@ -30495,11 +30700,11 @@
       </c>
       <c r="B227" s="113">
         <f t="shared" si="186"/>
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C227" s="113">
         <f t="shared" si="186"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D227" s="113">
         <f t="shared" si="187"/>
@@ -30511,11 +30716,11 @@
       </c>
       <c r="F227" s="138">
         <f>B227*29.11+C227*58.22</f>
-        <v>22472.92</v>
+        <v>22589.360000000001</v>
       </c>
       <c r="G227" s="138">
         <f t="shared" si="188"/>
-        <v>2337183.6799999997</v>
+        <v>2349293.44</v>
       </c>
       <c r="H227" s="138"/>
       <c r="I227" s="113" t="e">
@@ -30551,11 +30756,11 @@
       </c>
       <c r="B228" s="113">
         <f>B8+B15+B22+B29+B36+B43+B50+B57+B64+B71+B78+B85+B92+B99+B106+B113+B120+B127+B134+B141+B148+B155+B162+B169+B176+B183+B190+B197+B204+B211+B218</f>
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C228" s="113">
         <f>C8+C15+C22+C29+C36+C43+C50+C57+C64+C71+C78+C85+C92+C99+C106+C113+C120+C127+C134+C141+C148+C155+C162+C169+C176+C183+C190+C197+C204+C211+C219</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D228" s="113">
         <f t="shared" si="187"/>
@@ -30567,11 +30772,11 @@
       </c>
       <c r="F228" s="138">
         <f>B228*29.11+C228*58.22</f>
-        <v>20638.989999999998</v>
+        <v>20755.43</v>
       </c>
       <c r="G228" s="138">
         <f t="shared" si="188"/>
-        <v>2146454.96</v>
+        <v>2158564.7200000002</v>
       </c>
       <c r="H228" s="138"/>
       <c r="I228" s="113" t="e">
@@ -30751,11 +30956,11 @@
       </c>
       <c r="B232" s="278">
         <f>SUM(B225:B231)</f>
-        <v>4094</v>
+        <v>4066</v>
       </c>
       <c r="C232" s="278">
         <f>SUM(C225:C231)</f>
-        <v>1927</v>
+        <v>1955</v>
       </c>
       <c r="D232" s="278">
         <f>SUM(D225:D231)</f>
@@ -30767,11 +30972,11 @@
       </c>
       <c r="F232" s="278">
         <f>SUM(F225:F230)</f>
-        <v>320916.63</v>
+        <v>322012.11</v>
       </c>
       <c r="G232" s="278">
         <f>SUM(G225:G230)</f>
-        <v>33375329.520000003</v>
+        <v>33489259.439999998</v>
       </c>
       <c r="H232" s="278"/>
       <c r="I232" s="278" t="e">
@@ -30827,7 +31032,7 @@
       </c>
       <c r="C234" s="123">
         <f>(B232)+(C232*2)</f>
-        <v>7948</v>
+        <v>7976</v>
       </c>
       <c r="D234" s="123"/>
       <c r="E234" s="123"/>
@@ -30849,10 +31054,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="23"/>
-      <c r="B235" s="351" t="s">
+      <c r="B235" s="353" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="352"/>
+      <c r="C235" s="354"/>
       <c r="D235" s="24" t="s">
         <v>65</v>
       </c>
@@ -30922,12 +31127,12 @@
       </c>
       <c r="G237" s="35">
         <f>+F232</f>
-        <v>320916.63</v>
+        <v>322012.11</v>
       </c>
       <c r="H237" s="285"/>
       <c r="I237" s="36">
         <f>+G232</f>
-        <v>33375329.520000003</v>
+        <v>33489259.439999998</v>
       </c>
       <c r="J237" s="123"/>
       <c r="K237" s="123"/>
@@ -31368,130 +31573,130 @@
   <sheetData>
     <row r="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="375">
+      <c r="D1" s="377">
         <v>46296</v>
       </c>
-      <c r="E1" s="375"/>
-      <c r="F1" s="375">
+      <c r="E1" s="377"/>
+      <c r="F1" s="377">
         <v>46297</v>
       </c>
-      <c r="G1" s="375"/>
-      <c r="H1" s="375">
+      <c r="G1" s="377"/>
+      <c r="H1" s="377">
         <v>46298</v>
       </c>
-      <c r="I1" s="375"/>
-      <c r="J1" s="375">
+      <c r="I1" s="377"/>
+      <c r="J1" s="377">
         <v>46299</v>
       </c>
-      <c r="K1" s="375"/>
-      <c r="L1" s="375">
+      <c r="K1" s="377"/>
+      <c r="L1" s="377">
         <v>46300</v>
       </c>
-      <c r="M1" s="375"/>
-      <c r="N1" s="375">
+      <c r="M1" s="377"/>
+      <c r="N1" s="377">
         <v>46301</v>
       </c>
-      <c r="O1" s="375"/>
-      <c r="P1" s="375">
+      <c r="O1" s="377"/>
+      <c r="P1" s="377">
         <v>46302</v>
       </c>
-      <c r="Q1" s="375"/>
-      <c r="R1" s="375">
+      <c r="Q1" s="377"/>
+      <c r="R1" s="377">
         <v>46303</v>
       </c>
-      <c r="S1" s="375"/>
-      <c r="T1" s="375">
+      <c r="S1" s="377"/>
+      <c r="T1" s="377">
         <v>46304</v>
       </c>
-      <c r="U1" s="375"/>
-      <c r="V1" s="375">
+      <c r="U1" s="377"/>
+      <c r="V1" s="377">
         <v>46305</v>
       </c>
-      <c r="W1" s="375"/>
-      <c r="X1" s="375">
+      <c r="W1" s="377"/>
+      <c r="X1" s="377">
         <v>46306</v>
       </c>
-      <c r="Y1" s="375"/>
-      <c r="Z1" s="375">
+      <c r="Y1" s="377"/>
+      <c r="Z1" s="377">
         <v>46307</v>
       </c>
-      <c r="AA1" s="375"/>
-      <c r="AB1" s="375">
+      <c r="AA1" s="377"/>
+      <c r="AB1" s="377">
         <v>46308</v>
       </c>
-      <c r="AC1" s="375"/>
-      <c r="AD1" s="375">
+      <c r="AC1" s="377"/>
+      <c r="AD1" s="377">
         <v>46309</v>
       </c>
-      <c r="AE1" s="375"/>
-      <c r="AF1" s="375">
+      <c r="AE1" s="377"/>
+      <c r="AF1" s="377">
         <v>46310</v>
       </c>
-      <c r="AG1" s="375"/>
-      <c r="AH1" s="375">
+      <c r="AG1" s="377"/>
+      <c r="AH1" s="377">
         <v>46311</v>
       </c>
-      <c r="AI1" s="375"/>
-      <c r="AJ1" s="375">
+      <c r="AI1" s="377"/>
+      <c r="AJ1" s="377">
         <v>46312</v>
       </c>
-      <c r="AK1" s="375"/>
-      <c r="AL1" s="375">
+      <c r="AK1" s="377"/>
+      <c r="AL1" s="377">
         <v>46313</v>
       </c>
-      <c r="AM1" s="375"/>
-      <c r="AN1" s="375">
+      <c r="AM1" s="377"/>
+      <c r="AN1" s="377">
         <v>46314</v>
       </c>
-      <c r="AO1" s="375"/>
-      <c r="AP1" s="375">
+      <c r="AO1" s="377"/>
+      <c r="AP1" s="377">
         <v>46315</v>
       </c>
-      <c r="AQ1" s="375"/>
-      <c r="AR1" s="375">
+      <c r="AQ1" s="377"/>
+      <c r="AR1" s="377">
         <v>46316</v>
       </c>
-      <c r="AS1" s="375"/>
-      <c r="AT1" s="375">
+      <c r="AS1" s="377"/>
+      <c r="AT1" s="377">
         <v>46317</v>
       </c>
-      <c r="AU1" s="375"/>
-      <c r="AV1" s="375">
+      <c r="AU1" s="377"/>
+      <c r="AV1" s="377">
         <v>46318</v>
       </c>
-      <c r="AW1" s="375"/>
-      <c r="AX1" s="375">
+      <c r="AW1" s="377"/>
+      <c r="AX1" s="377">
         <v>46319</v>
       </c>
-      <c r="AY1" s="375"/>
-      <c r="AZ1" s="375">
+      <c r="AY1" s="377"/>
+      <c r="AZ1" s="377">
         <v>46320</v>
       </c>
-      <c r="BA1" s="375"/>
-      <c r="BB1" s="375">
+      <c r="BA1" s="377"/>
+      <c r="BB1" s="377">
         <v>46321</v>
       </c>
-      <c r="BC1" s="375"/>
-      <c r="BD1" s="375">
+      <c r="BC1" s="377"/>
+      <c r="BD1" s="377">
         <v>46322</v>
       </c>
-      <c r="BE1" s="375"/>
-      <c r="BF1" s="375">
+      <c r="BE1" s="377"/>
+      <c r="BF1" s="377">
         <v>46323</v>
       </c>
-      <c r="BG1" s="375"/>
-      <c r="BH1" s="375">
+      <c r="BG1" s="377"/>
+      <c r="BH1" s="377">
         <v>46324</v>
       </c>
-      <c r="BI1" s="375"/>
-      <c r="BJ1" s="375">
+      <c r="BI1" s="377"/>
+      <c r="BJ1" s="377">
         <v>46325</v>
       </c>
-      <c r="BK1" s="375"/>
-      <c r="BL1" s="375">
+      <c r="BK1" s="377"/>
+      <c r="BL1" s="377">
         <v>46326</v>
       </c>
-      <c r="BM1" s="375"/>
+      <c r="BM1" s="377"/>
     </row>
     <row r="2" spans="1:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -31844,10 +32049,18 @@
       <c r="BC3" s="295">
         <v>0</v>
       </c>
-      <c r="BD3" s="155"/>
-      <c r="BE3" s="155"/>
-      <c r="BF3" s="155"/>
-      <c r="BG3" s="295"/>
+      <c r="BD3" s="155">
+        <v>10</v>
+      </c>
+      <c r="BE3" s="155">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="155">
+        <v>9</v>
+      </c>
+      <c r="BG3" s="295">
+        <v>2</v>
+      </c>
       <c r="BH3" s="155"/>
       <c r="BI3" s="155"/>
       <c r="BJ3" s="155"/>
@@ -32017,10 +32230,18 @@
       <c r="BC4" s="295">
         <v>0</v>
       </c>
-      <c r="BD4" s="155"/>
-      <c r="BE4" s="155"/>
-      <c r="BF4" s="155"/>
-      <c r="BG4" s="295"/>
+      <c r="BD4" s="155">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="155">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="295">
+        <v>0</v>
+      </c>
       <c r="BH4" s="155"/>
       <c r="BI4" s="155"/>
       <c r="BJ4" s="155"/>
@@ -32190,10 +32411,18 @@
       <c r="BC5" s="295">
         <v>9</v>
       </c>
-      <c r="BD5" s="155"/>
-      <c r="BE5" s="155"/>
-      <c r="BF5" s="155"/>
-      <c r="BG5" s="295"/>
+      <c r="BD5" s="155">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="155">
+        <v>10</v>
+      </c>
+      <c r="BF5" s="155">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="295">
+        <v>10</v>
+      </c>
       <c r="BH5" s="155"/>
       <c r="BI5" s="155"/>
       <c r="BJ5" s="155"/>
@@ -32363,10 +32592,18 @@
       <c r="BC6" s="295">
         <v>0</v>
       </c>
-      <c r="BD6" s="155"/>
-      <c r="BE6" s="155"/>
-      <c r="BF6" s="155"/>
-      <c r="BG6" s="295"/>
+      <c r="BD6" s="155">
+        <v>10</v>
+      </c>
+      <c r="BE6" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="155">
+        <v>10</v>
+      </c>
+      <c r="BG6" s="295">
+        <v>0</v>
+      </c>
       <c r="BH6" s="155"/>
       <c r="BI6" s="155"/>
       <c r="BJ6" s="155"/>
@@ -32536,10 +32773,18 @@
       <c r="BC7" s="295">
         <v>0</v>
       </c>
-      <c r="BD7" s="155"/>
-      <c r="BE7" s="155"/>
-      <c r="BF7" s="155"/>
-      <c r="BG7" s="295"/>
+      <c r="BD7" s="155">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="155">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="295">
+        <v>0</v>
+      </c>
       <c r="BH7" s="155"/>
       <c r="BI7" s="155"/>
       <c r="BJ7" s="155"/>
@@ -32709,10 +32954,18 @@
       <c r="BC8" s="295">
         <v>8</v>
       </c>
-      <c r="BD8" s="155"/>
-      <c r="BE8" s="155"/>
-      <c r="BF8" s="155"/>
-      <c r="BG8" s="295"/>
+      <c r="BD8" s="155">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="155">
+        <v>9</v>
+      </c>
+      <c r="BF8" s="155">
+        <v>1</v>
+      </c>
+      <c r="BG8" s="295">
+        <v>9</v>
+      </c>
       <c r="BH8" s="155"/>
       <c r="BI8" s="155"/>
       <c r="BJ8" s="155"/>
@@ -32993,10 +33246,18 @@
       <c r="BC10" s="295">
         <v>0</v>
       </c>
-      <c r="BD10" s="155"/>
-      <c r="BE10" s="155"/>
-      <c r="BF10" s="155"/>
-      <c r="BG10" s="295"/>
+      <c r="BD10" s="155">
+        <v>17</v>
+      </c>
+      <c r="BE10" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="155">
+        <v>17</v>
+      </c>
+      <c r="BG10" s="295">
+        <v>0</v>
+      </c>
       <c r="BH10" s="155"/>
       <c r="BI10" s="155"/>
       <c r="BJ10" s="155"/>
@@ -33166,10 +33427,18 @@
       <c r="BC11" s="295">
         <v>0</v>
       </c>
-      <c r="BD11" s="155"/>
-      <c r="BE11" s="155"/>
-      <c r="BF11" s="155"/>
-      <c r="BG11" s="295"/>
+      <c r="BD11" s="155">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="155">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="295">
+        <v>0</v>
+      </c>
       <c r="BH11" s="155"/>
       <c r="BI11" s="155"/>
       <c r="BJ11" s="155"/>
@@ -33339,10 +33608,18 @@
       <c r="BC12" s="295">
         <v>26</v>
       </c>
-      <c r="BD12" s="155"/>
-      <c r="BE12" s="155"/>
-      <c r="BF12" s="155"/>
-      <c r="BG12" s="295"/>
+      <c r="BD12" s="155">
+        <v>35</v>
+      </c>
+      <c r="BE12" s="155">
+        <v>26</v>
+      </c>
+      <c r="BF12" s="155">
+        <v>35</v>
+      </c>
+      <c r="BG12" s="295">
+        <v>26</v>
+      </c>
       <c r="BH12" s="155"/>
       <c r="BI12" s="155"/>
       <c r="BJ12" s="155"/>
@@ -33532,10 +33809,18 @@
       <c r="BC13" s="295">
         <v>0</v>
       </c>
-      <c r="BD13" s="155"/>
-      <c r="BE13" s="155"/>
-      <c r="BF13" s="155"/>
-      <c r="BG13" s="295"/>
+      <c r="BD13" s="155">
+        <v>15</v>
+      </c>
+      <c r="BE13" s="155">
+        <v>1</v>
+      </c>
+      <c r="BF13" s="155">
+        <v>14</v>
+      </c>
+      <c r="BG13" s="295">
+        <v>2</v>
+      </c>
       <c r="BH13" s="155"/>
       <c r="BI13" s="155"/>
       <c r="BJ13" s="155"/>
@@ -33705,10 +33990,18 @@
       <c r="BC14" s="295">
         <v>0</v>
       </c>
-      <c r="BD14" s="155"/>
-      <c r="BE14" s="155"/>
-      <c r="BF14" s="155"/>
-      <c r="BG14" s="295"/>
+      <c r="BD14" s="155">
+        <v>3</v>
+      </c>
+      <c r="BE14" s="155">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="155">
+        <v>3</v>
+      </c>
+      <c r="BG14" s="295">
+        <v>0</v>
+      </c>
       <c r="BH14" s="155"/>
       <c r="BI14" s="155"/>
       <c r="BJ14" s="155"/>
@@ -33878,10 +34171,18 @@
       <c r="BC15" s="295">
         <v>32</v>
       </c>
-      <c r="BD15" s="155"/>
-      <c r="BE15" s="155"/>
-      <c r="BF15" s="155"/>
-      <c r="BG15" s="295"/>
+      <c r="BD15" s="155">
+        <v>29</v>
+      </c>
+      <c r="BE15" s="155">
+        <v>32</v>
+      </c>
+      <c r="BF15" s="155">
+        <v>29</v>
+      </c>
+      <c r="BG15" s="295">
+        <v>32</v>
+      </c>
       <c r="BH15" s="155"/>
       <c r="BI15" s="155"/>
       <c r="BJ15" s="155"/>
@@ -34162,10 +34463,18 @@
       <c r="BC17" s="320">
         <v>0</v>
       </c>
-      <c r="BD17" s="280"/>
-      <c r="BE17" s="321"/>
-      <c r="BF17" s="280"/>
-      <c r="BG17" s="321"/>
+      <c r="BD17" s="280">
+        <v>7</v>
+      </c>
+      <c r="BE17" s="321">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="280">
+        <v>7</v>
+      </c>
+      <c r="BG17" s="321">
+        <v>0</v>
+      </c>
       <c r="BH17" s="280"/>
       <c r="BI17" s="321"/>
       <c r="BJ17" s="155"/>
@@ -34335,10 +34644,18 @@
       <c r="BC18" s="318">
         <v>0</v>
       </c>
-      <c r="BD18" s="280"/>
-      <c r="BE18" s="321"/>
-      <c r="BF18" s="280"/>
-      <c r="BG18" s="321"/>
+      <c r="BD18" s="280">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="321">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="280">
+        <v>0</v>
+      </c>
+      <c r="BG18" s="321">
+        <v>0</v>
+      </c>
       <c r="BH18" s="280"/>
       <c r="BI18" s="321"/>
       <c r="BJ18" s="155"/>
@@ -34508,10 +34825,18 @@
       <c r="BC19" s="318">
         <v>7</v>
       </c>
-      <c r="BD19" s="280"/>
-      <c r="BE19" s="321"/>
-      <c r="BF19" s="280"/>
-      <c r="BG19" s="321"/>
+      <c r="BD19" s="280">
+        <v>1</v>
+      </c>
+      <c r="BE19" s="321">
+        <v>7</v>
+      </c>
+      <c r="BF19" s="280">
+        <v>1</v>
+      </c>
+      <c r="BG19" s="321">
+        <v>7</v>
+      </c>
       <c r="BH19" s="280"/>
       <c r="BI19" s="321"/>
       <c r="BJ19" s="155"/>
@@ -34681,10 +35006,18 @@
       <c r="BC20" s="155">
         <v>0</v>
       </c>
-      <c r="BD20" s="280"/>
-      <c r="BE20" s="321"/>
-      <c r="BF20" s="280"/>
-      <c r="BG20" s="321"/>
+      <c r="BD20" s="280">
+        <v>6</v>
+      </c>
+      <c r="BE20" s="321">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="280">
+        <v>6</v>
+      </c>
+      <c r="BG20" s="321">
+        <v>0</v>
+      </c>
       <c r="BH20" s="280"/>
       <c r="BI20" s="321"/>
       <c r="BJ20" s="155"/>
@@ -34854,10 +35187,18 @@
       <c r="BC21" s="155">
         <v>0</v>
       </c>
-      <c r="BD21" s="280"/>
-      <c r="BE21" s="321"/>
-      <c r="BF21" s="280"/>
-      <c r="BG21" s="321"/>
+      <c r="BD21" s="280">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="321">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="280">
+        <v>0</v>
+      </c>
+      <c r="BG21" s="321">
+        <v>0</v>
+      </c>
       <c r="BH21" s="280"/>
       <c r="BI21" s="321"/>
       <c r="BJ21" s="155"/>
@@ -35027,10 +35368,18 @@
       <c r="BC22" s="155">
         <v>3</v>
       </c>
-      <c r="BD22" s="280"/>
-      <c r="BE22" s="321"/>
-      <c r="BF22" s="280"/>
-      <c r="BG22" s="321"/>
+      <c r="BD22" s="280">
+        <v>4</v>
+      </c>
+      <c r="BE22" s="321">
+        <v>3</v>
+      </c>
+      <c r="BF22" s="280">
+        <v>4</v>
+      </c>
+      <c r="BG22" s="321">
+        <v>3</v>
+      </c>
       <c r="BH22" s="280"/>
       <c r="BI22" s="321"/>
       <c r="BJ22" s="155"/>
@@ -35315,19 +35664,19 @@
       </c>
       <c r="BD24" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="BE24" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="BF24" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="BG24" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="BH24" s="136">
         <f t="shared" si="3"/>
@@ -35787,19 +36136,19 @@
       </c>
       <c r="BD31" s="257">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE31" s="257">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="BF31" s="172">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG31" s="172">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="BH31" s="310">
         <f t="shared" si="6"/>
@@ -36041,19 +36390,19 @@
       </c>
       <c r="BD32" s="257">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE32" s="257">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF32" s="172">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG32" s="172">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BH32" s="310">
         <f t="shared" si="9"/>
@@ -36295,19 +36644,19 @@
       </c>
       <c r="BD33" s="257">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE33" s="257">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF33" s="247">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="BG33" s="172">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH33" s="310">
         <f t="shared" si="12"/>
@@ -36549,19 +36898,19 @@
       </c>
       <c r="BD34" s="257">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="BE34" s="257">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF34" s="172">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG34" s="172">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH34" s="310">
         <f t="shared" si="15"/>
@@ -37057,7 +37406,7 @@
       </c>
       <c r="BD36" s="257">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE36" s="257">
         <f t="shared" si="21"/>
@@ -37065,7 +37414,7 @@
       </c>
       <c r="BF36" s="172">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG36" s="172">
         <f t="shared" si="21"/>
@@ -37097,10 +37446,10 @@
       </c>
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A37" s="376" t="s">
+      <c r="A37" s="378" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="376"/>
+      <c r="B37" s="378"/>
       <c r="C37" s="8"/>
       <c r="D37" s="148">
         <f t="shared" ref="D37:AI37" si="23">SUM(D31:D36)</f>
@@ -37312,19 +37661,19 @@
       </c>
       <c r="BD37" s="309">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="BE37" s="309">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="BF37" s="309">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="BG37" s="309">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="BH37" s="310">
         <f t="shared" ref="BH37:BK37" si="25">SUM(BH31:BH36)</f>
@@ -37578,12 +37927,12 @@
       <c r="BC40" s="257"/>
       <c r="BD40" s="257">
         <f>BD5+BE5+BD12+BE12+BD19+BE19</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="BE40" s="114"/>
       <c r="BF40" s="56">
         <f>BF5+BG5+BF12+BG12+BF19+BG19</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="BG40" s="258"/>
       <c r="BH40" s="310">
@@ -37739,12 +38088,12 @@
       <c r="BC41" s="257"/>
       <c r="BD41" s="257">
         <f>BD8+BE8+BD15+BE15+BD22+BE22</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BE41" s="114"/>
       <c r="BF41" s="56">
         <f>BF8+BG8+BF15+BG15+BF22+BG22</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BG41" s="258"/>
       <c r="BH41" s="310">
@@ -37900,12 +38249,12 @@
       <c r="BC42" s="257"/>
       <c r="BD42" s="257">
         <f>BD3+BE3+BD10+BE10+BD17+BE17</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="BE42" s="114"/>
       <c r="BF42" s="56">
         <f>BF3+BG3+BF10+BG10+BF17+BG17</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="BG42" s="258"/>
       <c r="BH42" s="310">
@@ -38061,12 +38410,12 @@
       <c r="BC43" s="257"/>
       <c r="BD43" s="257">
         <f>BD6+BE6+BD13+BE13+BD20+BE20</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE43" s="114"/>
       <c r="BF43" s="56">
         <f>BF6+BG6+BF13+BG13+BF20+BG20</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BG43" s="258"/>
       <c r="BH43" s="310">
@@ -38383,12 +38732,12 @@
       <c r="BC45" s="309"/>
       <c r="BD45" s="257">
         <f>BD7+BE7+BD14+BE14+BD21+BE21</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE45" s="309"/>
       <c r="BF45" s="56">
         <f>BF7+BG7+BF14+BG14+BF21+BG21</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG45" s="258"/>
       <c r="BH45" s="310">
@@ -38678,12 +39027,12 @@
       <c r="BC48" s="257"/>
       <c r="BD48" s="257">
         <f>(BD5+BD12+BD19)+2*(BE5+BE12+BE19)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="BE48" s="116"/>
       <c r="BF48" s="56">
         <f>(BF5+BF12+BF19)+2*(BG5+BG12+BG19)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="BG48" s="258"/>
       <c r="BH48" s="310">
@@ -38839,12 +39188,12 @@
       <c r="BC49" s="257"/>
       <c r="BD49" s="257">
         <f>(BD8+BD15+BD22)+2*(BE8+BE15+BE22)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="BE49" s="116"/>
       <c r="BF49" s="56">
         <f>(BF8+BF15+BF22)+2*(BG8+BG15+BG22)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="BG49" s="258"/>
       <c r="BH49" s="310">
@@ -39000,12 +39349,12 @@
       <c r="BC50" s="257"/>
       <c r="BD50" s="257">
         <f>(BD3+BD10+BD17)+2*(BE3+BE10+BE17)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE50" s="116"/>
       <c r="BF50" s="56">
         <f>(BF3+BF10+BF17)+2*(BG3+BG10+BG17)</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="BG50" s="258"/>
       <c r="BH50" s="310">
@@ -39161,12 +39510,12 @@
       <c r="BC51" s="257"/>
       <c r="BD51" s="257">
         <f>(BD6+BD13+BD20)+2*(BE6+BE13+BE20)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="BE51" s="116"/>
       <c r="BF51" s="56">
         <f>(BF6+BF13+BF20)+2*(BG6+BG13+BG20)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG51" s="258"/>
       <c r="BH51" s="310">
@@ -39483,12 +39832,12 @@
       <c r="BC53" s="309"/>
       <c r="BD53" s="257">
         <f>(BD7+BD14+BD21)+2*(BE7+BE14+BE21)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE53" s="309"/>
       <c r="BF53" s="56">
         <f>(BF7+BF14+BF21)+2*(BG7+BG14+BG21)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG53" s="258"/>
       <c r="BH53" s="310">
@@ -39529,7 +39878,7 @@
       <c r="AR59" s="123"/>
       <c r="AS59" s="123"/>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="W60" s="123"/>
       <c r="X60" s="123"/>
       <c r="Y60" s="123"/>
@@ -39554,65 +39903,61 @@
       <c r="AR60" s="123"/>
       <c r="AS60" s="123"/>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="R61" s="123">
-        <v>11</v>
-      </c>
-      <c r="S61" s="123">
-        <v>0</v>
-      </c>
-      <c r="T61" s="123">
+    <row r="61" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R61" s="350">
+        <v>9</v>
+      </c>
+      <c r="S61" s="350">
+        <v>0</v>
+      </c>
+      <c r="T61" s="350">
+        <v>0</v>
+      </c>
+      <c r="U61" s="350">
+        <v>10</v>
+      </c>
+      <c r="V61" s="350">
+        <v>0</v>
+      </c>
+      <c r="W61" s="350">
         <v>1</v>
       </c>
-      <c r="U61" s="123">
-        <v>10</v>
-      </c>
-      <c r="V61" s="123">
-        <v>0</v>
-      </c>
-      <c r="W61" s="123">
-        <v>2</v>
-      </c>
-      <c r="X61" s="123" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y61" s="123">
+      <c r="X61" s="351"/>
+      <c r="Y61" s="351">
         <v>17</v>
       </c>
-      <c r="Z61" s="123">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="123">
+      <c r="Z61" s="351">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="351">
         <v>35</v>
       </c>
-      <c r="AB61" s="123">
-        <v>16</v>
-      </c>
-      <c r="AC61" s="123">
+      <c r="AB61" s="351">
+        <v>14</v>
+      </c>
+      <c r="AC61" s="351">
         <v>3</v>
       </c>
-      <c r="AD61" s="123">
+      <c r="AD61" s="351">
         <v>29</v>
       </c>
-      <c r="AE61" s="123" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF61" s="123">
+      <c r="AE61" s="351"/>
+      <c r="AF61" s="350">
         <v>7</v>
       </c>
-      <c r="AG61" s="123">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="123">
+      <c r="AG61" s="350">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="350">
         <v>1</v>
       </c>
-      <c r="AI61" s="123">
+      <c r="AI61" s="350">
         <v>6</v>
       </c>
-      <c r="AJ61" s="123">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="123">
+      <c r="AJ61" s="350">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="350">
         <v>4</v>
       </c>
       <c r="AL61" s="123"/>
@@ -39628,65 +39973,61 @@
       <c r="AV61" s="123"/>
       <c r="AW61" s="123"/>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="R62" s="123">
-        <v>0</v>
-      </c>
-      <c r="S62" s="123">
-        <v>0</v>
-      </c>
-      <c r="T62" s="123">
+    <row r="62" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R62" s="350">
+        <v>2</v>
+      </c>
+      <c r="S62" s="350">
+        <v>0</v>
+      </c>
+      <c r="T62" s="350">
+        <v>10</v>
+      </c>
+      <c r="U62" s="350">
+        <v>0</v>
+      </c>
+      <c r="V62" s="350">
+        <v>0</v>
+      </c>
+      <c r="W62" s="350">
         <v>9</v>
       </c>
-      <c r="U62" s="123">
-        <v>0</v>
-      </c>
-      <c r="V62" s="123">
-        <v>0</v>
-      </c>
-      <c r="W62" s="123">
-        <v>8</v>
-      </c>
-      <c r="X62" s="123" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y62" s="123">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="123">
+      <c r="X62" s="351"/>
+      <c r="Y62" s="351">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="351">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="351">
         <v>26</v>
       </c>
-      <c r="AB62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="123">
+      <c r="AB62" s="351">
+        <v>2</v>
+      </c>
+      <c r="AC62" s="351">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="351">
         <v>32</v>
       </c>
-      <c r="AE62" s="123" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AG62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AH62" s="123">
+      <c r="AE62" s="351"/>
+      <c r="AF62" s="350">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="350">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="350">
         <v>7</v>
       </c>
-      <c r="AI62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="123">
-        <v>0</v>
-      </c>
-      <c r="AK62" s="123">
+      <c r="AI62" s="350">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="350">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="350">
         <v>3</v>
       </c>
       <c r="AL62" s="123"/>
@@ -40008,11 +40349,11 @@
       </c>
       <c r="AC5" s="94">
         <f>'Data Ocupacion'!BD40</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AD5" s="94">
         <f>'Data Ocupacion'!BF40</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AE5" s="94">
         <f>'Data Ocupacion'!BH40</f>
@@ -40140,11 +40481,11 @@
       </c>
       <c r="AC6" s="94">
         <f>'Data Ocupacion'!BD41</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AD6" s="94">
         <f>'Data Ocupacion'!BF41</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AE6" s="94">
         <f>'Data Ocupacion'!BH41</f>
@@ -40272,11 +40613,11 @@
       </c>
       <c r="AC7" s="94">
         <f>'Data Ocupacion'!BD42</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AD7" s="94">
         <f>'Data Ocupacion'!BF42</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AE7" s="94">
         <f>'Data Ocupacion'!BH42</f>
@@ -40404,11 +40745,11 @@
       </c>
       <c r="AC8" s="94">
         <f>'Data Ocupacion'!BD43</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AD8" s="94">
         <f>'Data Ocupacion'!BF43</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE8" s="94">
         <f>'Data Ocupacion'!BH43</f>
@@ -40668,11 +41009,11 @@
       </c>
       <c r="AC10" s="94">
         <f>'Data Ocupacion'!BD45</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10" s="94">
         <f>'Data Ocupacion'!BF45</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE10" s="94">
         <f>'Data Ocupacion'!BH45</f>
@@ -40829,11 +41170,11 @@
       </c>
       <c r="AC12" s="94">
         <f>'Data Ocupacion'!BD48</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AD12" s="94">
         <f>'Data Ocupacion'!BF48</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AE12" s="94">
         <f>'Data Ocupacion'!BH48</f>
@@ -40961,11 +41302,11 @@
       </c>
       <c r="AC13" s="94">
         <f>'Data Ocupacion'!BD49</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AD13" s="94">
         <f>'Data Ocupacion'!BF49</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AE13" s="94">
         <f>'Data Ocupacion'!BH49</f>
@@ -41093,11 +41434,11 @@
       </c>
       <c r="AC14" s="94">
         <f>'Data Ocupacion'!BD50</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AD14" s="94">
         <f>'Data Ocupacion'!BF50</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AE14" s="94">
         <f>'Data Ocupacion'!BH50</f>
@@ -41225,11 +41566,11 @@
       </c>
       <c r="AC15" s="94">
         <f>'Data Ocupacion'!BD51</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AD15" s="94">
         <f>'Data Ocupacion'!BF51</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE15" s="94">
         <f>'Data Ocupacion'!BH51</f>
@@ -41357,11 +41698,11 @@
       </c>
       <c r="AC16" s="94">
         <f>'Data Ocupacion'!BD53</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD16" s="94">
         <f>'Data Ocupacion'!BF53</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="94">
         <f>'Data Ocupacion'!BH53</f>
@@ -41623,11 +41964,11 @@
       </c>
       <c r="AC19" s="82">
         <f>'KM-Servicio'!Q187</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19" s="82">
         <f>'KM-Servicio'!Q194</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" s="82">
         <f>'KM-Servicio'!Q201</f>
@@ -41755,11 +42096,11 @@
       </c>
       <c r="AC20" s="82">
         <f>'KM-Servicio'!T188</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD20" s="82">
         <f>'KM-Servicio'!T195</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE20" s="82">
         <f>'KM-Servicio'!T202</f>
@@ -41986,7 +42327,7 @@
         <v>1</v>
       </c>
       <c r="X22" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="82">
         <v>0</v>
@@ -42001,10 +42342,10 @@
         <v>0</v>
       </c>
       <c r="AC22" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" s="82">
         <v>0</v>
@@ -42174,7 +42515,7 @@
       </c>
       <c r="B27" s="223">
         <f t="shared" ref="B27:B34" si="0">SUM(C27:AG27)</f>
-        <v>4998</v>
+        <v>5452</v>
       </c>
       <c r="C27" s="90">
         <f t="shared" ref="C27:AF27" si="1">SUM(C5:C10)</f>
@@ -42282,11 +42623,11 @@
       </c>
       <c r="AC27" s="90">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="AD27" s="90">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="AE27" s="90">
         <f t="shared" si="1"/>
@@ -42307,7 +42648,7 @@
       </c>
       <c r="B28" s="223">
         <f t="shared" si="0"/>
-        <v>6528</v>
+        <v>7162</v>
       </c>
       <c r="C28" s="90">
         <f t="shared" ref="C28:AF28" si="3">SUM(C12:C17)</f>
@@ -42415,11 +42756,11 @@
       </c>
       <c r="AC28" s="90">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="AD28" s="90">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="AE28" s="90">
         <f t="shared" si="3"/>
@@ -42440,7 +42781,7 @@
       </c>
       <c r="B29" s="223">
         <f t="shared" si="0"/>
-        <v>262347.90000000002</v>
+        <v>287441.31</v>
       </c>
       <c r="C29" s="90">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42528,7 +42869,7 @@
       </c>
       <c r="X29" s="90">
         <f t="shared" si="5"/>
-        <v>12474.090000000002</v>
+        <v>12462.960000000003</v>
       </c>
       <c r="Y29" s="90">
         <f t="shared" si="5"/>
@@ -42548,11 +42889,11 @@
       </c>
       <c r="AC29" s="90">
         <f>(AC12*$B$12+AC13*$B$13+AC14*$B$14+AC15*$B$15+AC17*$B$17+AC20*$B$20+AC16*$B$16+AC19*$B$19+AC21*$B$21+AC22*$B$22)</f>
-        <v>0</v>
+        <v>12533.880000000001</v>
       </c>
       <c r="AD29" s="90">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12570.660000000002</v>
       </c>
       <c r="AE29" s="90">
         <f>(AE12*$B$12+AE13*$B$13+AE14*$B$14+AE15*$B$15+AE17*$B$17+AE20*$B$20+AE16*$B$16+AE19*$B$19+AE21*$B$21+AE22*$B$22)</f>
@@ -42573,7 +42914,7 @@
       </c>
       <c r="B30" s="223">
         <f t="shared" si="0"/>
-        <v>198754.23000000007</v>
+        <v>216350.19000000009</v>
       </c>
       <c r="C30" s="90">
         <f t="shared" ref="C30:AF30" si="7">$B$5*C5+$B$6*C6+$B$7*C7+$B$8*C8+$B$10*C10+$B$9*C9</f>
@@ -42681,11 +43022,11 @@
       </c>
       <c r="AC30" s="90">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8797.9800000000014</v>
       </c>
       <c r="AD30" s="90">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8797.9800000000014</v>
       </c>
       <c r="AE30" s="90">
         <f t="shared" si="7"/>
@@ -42706,7 +43047,7 @@
       </c>
       <c r="B31" s="223">
         <f t="shared" si="0"/>
-        <v>27284181.600000001</v>
+        <v>29893896.240000002</v>
       </c>
       <c r="C31" s="90">
         <f t="shared" ref="C31:AD31" si="9">C29*104</f>
@@ -42794,7 +43135,7 @@
       </c>
       <c r="X31" s="90">
         <f t="shared" si="9"/>
-        <v>1297305.3600000001</v>
+        <v>1296147.8400000003</v>
       </c>
       <c r="Y31" s="90">
         <f t="shared" si="9"/>
@@ -42814,11 +43155,11 @@
       </c>
       <c r="AC31" s="90">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1303523.52</v>
       </c>
       <c r="AD31" s="90">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1307348.6400000001</v>
       </c>
       <c r="AE31" s="90">
         <f t="shared" ref="AE31" si="10">AE29*104</f>
@@ -42839,7 +43180,7 @@
       </c>
       <c r="B32" s="88">
         <f t="shared" si="0"/>
-        <v>524695.80000000005</v>
+        <v>574882.62</v>
       </c>
       <c r="C32" s="90">
         <f>C29*2</f>
@@ -42927,7 +43268,7 @@
       </c>
       <c r="X32" s="90">
         <f t="shared" si="13"/>
-        <v>24948.180000000004</v>
+        <v>24925.920000000006</v>
       </c>
       <c r="Y32" s="90">
         <f t="shared" si="13"/>
@@ -42947,11 +43288,11 @@
       </c>
       <c r="AC32" s="90">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>25067.760000000002</v>
       </c>
       <c r="AD32" s="90">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>25141.320000000003</v>
       </c>
       <c r="AE32" s="90">
         <f t="shared" ref="AE32" si="14">AE29*2</f>
@@ -42972,7 +43313,7 @@
       </c>
       <c r="B33" s="88">
         <f t="shared" si="0"/>
-        <v>2363136</v>
+        <v>2592644</v>
       </c>
       <c r="C33" s="90">
         <f>+C28*362</f>
@@ -43080,11 +43421,11 @@
       </c>
       <c r="AC33" s="90">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>114392</v>
       </c>
       <c r="AD33" s="90">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>115116</v>
       </c>
       <c r="AE33" s="90">
         <f t="shared" ref="AE33" si="18">+AE28*362</f>
@@ -43105,7 +43446,7 @@
       </c>
       <c r="B34" s="223">
         <f t="shared" si="0"/>
-        <v>20804188.470000003</v>
+        <v>22794095.883000001</v>
       </c>
       <c r="C34" s="90">
         <f>C29*79.3</f>
@@ -43193,7 +43534,7 @@
       </c>
       <c r="X34" s="90">
         <f t="shared" si="21"/>
-        <v>989195.33700000017</v>
+        <v>988312.72800000024</v>
       </c>
       <c r="Y34" s="90">
         <f t="shared" si="21"/>
@@ -43213,11 +43554,11 @@
       </c>
       <c r="AC34" s="90">
         <f>AC29*79.3</f>
-        <v>0</v>
+        <v>993936.68400000001</v>
       </c>
       <c r="AD34" s="90">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>996853.33800000011</v>
       </c>
       <c r="AE34" s="90">
         <f t="shared" ref="AE34" si="22">AE29*79.3</f>
@@ -43543,19 +43884,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="379" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
-      <c r="G2" s="378"/>
-      <c r="H2" s="378"/>
-      <c r="I2" s="378"/>
-      <c r="J2" s="378"/>
-      <c r="K2" s="378"/>
+      <c r="B2" s="380"/>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
+      <c r="F2" s="380"/>
+      <c r="G2" s="380"/>
+      <c r="H2" s="380"/>
+      <c r="I2" s="380"/>
+      <c r="J2" s="380"/>
+      <c r="K2" s="380"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="157" t="s">
@@ -44507,7 +44848,7 @@
       </c>
       <c r="I25" s="12">
         <f>'Oferta Diaria'!X34</f>
-        <v>989195.33700000017</v>
+        <v>988312.72800000024</v>
       </c>
       <c r="J25" s="160" t="s">
         <v>137</v>
@@ -44689,23 +45030,23 @@
       </c>
       <c r="B30" s="303">
         <f>'KM-Servicio'!N193</f>
-        <v>-65173616</v>
+        <v>13267</v>
       </c>
       <c r="C30" s="303">
         <f t="shared" si="0"/>
-        <v>-64898411</v>
+        <v>288472</v>
       </c>
       <c r="D30" s="303">
         <f>'KM-Servicio'!$W$193</f>
-        <v>0</v>
+        <v>12533.880000000003</v>
       </c>
       <c r="E30" s="303">
         <f t="shared" si="1"/>
-        <v>262336.77</v>
+        <v>274870.65000000002</v>
       </c>
       <c r="F30" s="304">
         <f>'KM-Servicio'!O193</f>
-        <v>0</v>
+        <v>94.474108690736429</v>
       </c>
       <c r="G30" s="305">
         <f>SUM('KM-Servicio'!B193:C193)</f>
@@ -44713,11 +45054,11 @@
       </c>
       <c r="H30" s="305">
         <f>SUM('KM-Servicio'!D193:E193)</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I30" s="303">
         <f>'Oferta Diaria'!AC34</f>
-        <v>0</v>
+        <v>993936.68400000001</v>
       </c>
       <c r="J30" s="160" t="s">
         <v>137</v>
@@ -44731,23 +45072,23 @@
       </c>
       <c r="B31" s="303">
         <f>'KM-Servicio'!N200</f>
-        <v>0</v>
+        <v>13234</v>
       </c>
       <c r="C31" s="303">
         <f t="shared" si="0"/>
-        <v>-64898411</v>
+        <v>301706</v>
       </c>
       <c r="D31" s="303">
         <f>'KM-Servicio'!$W$200</f>
-        <v>0</v>
+        <v>12570.660000000002</v>
       </c>
       <c r="E31" s="303">
         <f t="shared" si="1"/>
-        <v>262336.77</v>
-      </c>
-      <c r="F31" s="304" t="e">
+        <v>287441.31</v>
+      </c>
+      <c r="F31" s="304">
         <f>'KM-Servicio'!O200</f>
-        <v>#DIV/0!</v>
+        <v>94.987607677195115</v>
       </c>
       <c r="G31" s="305">
         <f>SUM('KM-Servicio'!B200:C200)</f>
@@ -44755,11 +45096,11 @@
       </c>
       <c r="H31" s="305">
         <f>SUM('KM-Servicio'!D200:E200)</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I31" s="303">
         <f>'Oferta Diaria'!AD34</f>
-        <v>0</v>
+        <v>996853.33800000011</v>
       </c>
       <c r="J31" s="160" t="s">
         <v>137</v>
@@ -44773,7 +45114,7 @@
       </c>
       <c r="B32" s="303">
         <f>'KM-Servicio'!N207</f>
-        <v>0</v>
+        <v>-65200117</v>
       </c>
       <c r="C32" s="303">
         <f t="shared" si="0"/>
@@ -44785,11 +45126,11 @@
       </c>
       <c r="E32" s="303">
         <f t="shared" si="1"/>
-        <v>262336.77</v>
-      </c>
-      <c r="F32" s="304" t="e">
+        <v>287441.31</v>
+      </c>
+      <c r="F32" s="304">
         <f>'KM-Servicio'!O207</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G32" s="165">
         <f>'KM-Servicio'!B207+'KM-Servicio'!C207</f>
@@ -44827,7 +45168,7 @@
       </c>
       <c r="E33" s="303">
         <f t="shared" si="1"/>
-        <v>262336.77</v>
+        <v>287441.31</v>
       </c>
       <c r="F33" s="164" t="e">
         <f>'KM-Servicio'!O214</f>
@@ -44871,7 +45212,7 @@
       </c>
       <c r="E34" s="303">
         <f t="shared" ref="E34" si="3">D34+E33</f>
-        <v>262336.77</v>
+        <v>287441.31</v>
       </c>
       <c r="F34" s="164">
         <f>'KM-Servicio'!O215</f>
@@ -44923,15 +45264,15 @@
       </c>
       <c r="C36" s="167">
         <f>SUM(C4:C34)</f>
-        <v>-320743547</v>
+        <v>-190356547</v>
       </c>
       <c r="D36" s="167">
         <f>SUM(D4:D34)</f>
-        <v>262336.77</v>
+        <v>287441.31</v>
       </c>
       <c r="E36" s="167">
         <f>SUM(E4:E34)</f>
-        <v>4882209.879999999</v>
+        <v>4995161.919999999</v>
       </c>
       <c r="F36" s="168" t="e">
         <f>AVERAGE(F4:F34)</f>
@@ -44947,7 +45288,7 @@
       </c>
       <c r="I36" s="167">
         <f>SUM(I4:I34)</f>
-        <v>20804188.470000003</v>
+        <v>22794095.883000001</v>
       </c>
       <c r="J36" s="29"/>
       <c r="K36" s="166"/>
@@ -44979,12 +45320,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="382" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="381"/>
-      <c r="C3" s="381"/>
-      <c r="D3" s="382"/>
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="384"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="95" t="s">
@@ -45014,7 +45355,7 @@
       </c>
       <c r="D5" s="129">
         <f>'KM-Servicio'!C234</f>
-        <v>7948</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -45048,7 +45389,7 @@
       </c>
       <c r="D7" s="129">
         <f>'KM-Servicio'!F232</f>
-        <v>320916.63</v>
+        <v>322012.11</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -45082,7 +45423,7 @@
       </c>
       <c r="D9" s="129">
         <f>'KM-Servicio'!G232</f>
-        <v>33375329.520000003</v>
+        <v>33489259.439999998</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -45130,12 +45471,12 @@
       <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="383" t="s">
+      <c r="A13" s="385" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="384"/>
-      <c r="C13" s="384"/>
-      <c r="D13" s="385"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="386"/>
+      <c r="D13" s="387"/>
       <c r="F13" s="139"/>
       <c r="G13" s="140"/>
       <c r="H13" s="140"/>
@@ -45182,8 +45523,8 @@
       <c r="C16" s="105"/>
       <c r="D16" s="106"/>
       <c r="F16" s="139"/>
-      <c r="G16" s="379"/>
-      <c r="H16" s="379"/>
+      <c r="G16" s="381"/>
+      <c r="H16" s="381"/>
       <c r="I16" s="139"/>
       <c r="J16" s="139"/>
       <c r="K16" s="139"/>
@@ -45198,8 +45539,8 @@
       <c r="C17" s="105"/>
       <c r="D17" s="106"/>
       <c r="F17" s="139"/>
-      <c r="G17" s="379"/>
-      <c r="H17" s="379"/>
+      <c r="G17" s="381"/>
+      <c r="H17" s="381"/>
       <c r="I17" s="139"/>
       <c r="J17" s="140"/>
       <c r="K17" s="140"/>
@@ -45214,8 +45555,8 @@
       <c r="C18" s="105"/>
       <c r="D18" s="106"/>
       <c r="F18" s="139"/>
-      <c r="G18" s="379"/>
-      <c r="H18" s="379"/>
+      <c r="G18" s="381"/>
+      <c r="H18" s="381"/>
       <c r="I18" s="140"/>
       <c r="J18" s="140"/>
       <c r="K18" s="42"/>
@@ -45229,8 +45570,8 @@
       <c r="C19" s="110"/>
       <c r="D19" s="106"/>
       <c r="F19" s="139"/>
-      <c r="G19" s="379"/>
-      <c r="H19" s="379"/>
+      <c r="G19" s="381"/>
+      <c r="H19" s="381"/>
       <c r="I19" s="140"/>
       <c r="J19" s="140"/>
       <c r="K19" s="42"/>
@@ -45244,8 +45585,8 @@
       <c r="C20" s="105"/>
       <c r="D20" s="106"/>
       <c r="F20" s="139"/>
-      <c r="G20" s="379"/>
-      <c r="H20" s="379"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
       <c r="I20" s="140"/>
       <c r="J20" s="140"/>
       <c r="K20" s="42"/>
@@ -45259,8 +45600,8 @@
       <c r="C21" s="105"/>
       <c r="D21" s="106"/>
       <c r="F21" s="139"/>
-      <c r="G21" s="379"/>
-      <c r="H21" s="379"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
       <c r="I21" s="139"/>
       <c r="J21" s="42"/>
       <c r="K21" s="42"/>
@@ -45285,9 +45626,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="107"/>
-      <c r="B23" s="386"/>
-      <c r="C23" s="387"/>
-      <c r="D23" s="388"/>
+      <c r="B23" s="388"/>
+      <c r="C23" s="389"/>
+      <c r="D23" s="390"/>
       <c r="F23" s="142"/>
       <c r="G23" s="140"/>
       <c r="H23" s="140"/>
@@ -45299,10 +45640,10 @@
       <c r="N23" s="42"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="383"/>
-      <c r="B24" s="384"/>
-      <c r="C24" s="384"/>
-      <c r="D24" s="385"/>
+      <c r="A24" s="385"/>
+      <c r="B24" s="386"/>
+      <c r="C24" s="386"/>
+      <c r="D24" s="387"/>
       <c r="F24" s="140"/>
       <c r="G24" s="140"/>
       <c r="H24" s="140"/>
@@ -45415,9 +45756,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="105"/>
-      <c r="B34" s="386"/>
-      <c r="C34" s="387"/>
-      <c r="D34" s="388"/>
+      <c r="B34" s="388"/>
+      <c r="C34" s="389"/>
+      <c r="D34" s="390"/>
       <c r="F34" s="99"/>
       <c r="I34" s="109"/>
     </row>
